--- a/skills/dataiku-diagnosis-checklist-review/resources/checklist_template.xlsx
+++ b/skills/dataiku-diagnosis-checklist-review/resources/checklist_template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Architecture, Compute &amp; Infrast" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Enterprise-grade Security, Perm" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Generative AI Acceleration &amp; In" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Scalable Performance, Stability" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Advanced Security Options (DSS " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture, Compute &amp; Infrast" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enterprise-grade Security, Perm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generative AI Acceleration &amp; In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalable Performance, Stability" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Advanced Security Options (DSS " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,26 +446,27 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
     <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,100 +502,105 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>statement_short</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>parameter_hint</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>operator</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>expected_value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>expected_condition_notes</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>supporting_evidence</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>contradicting_evidence</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>insufficient_evidence_handling</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rationale</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dataiku_concepts</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>source_document</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>source_page</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ambiguity_notes</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>validation_status</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>evidence_found</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>validated_by</t>
         </is>
@@ -631,62 +637,67 @@
           <t>Production-grade Dataiku deployments should separate experimental/design work from production runs by leveraging dedicated automation nodes; reviewers should discuss the Design -&gt; Deployer -&gt; Automation Node architecture with the customer and flag gaps, even though standing up new nodes is out of scope for the review itself.</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Separate production workloads onto dedicated automation nodes rather than running everything on the design node.</t>
+        </is>
+      </c>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Diagnosis shows a distinct automation node (or nodes) separate from the design node, with a deployer configured and bundles being pushed from design to automation.</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Only a single design node is used to run both experimentation and production workloads, with no automation node or deployer in use.</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not expose node topology/roles, flag needs_manual_review and recommend discussing the Design -&gt; Deployer -&gt; Automation architecture directly with the customer.</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>Mixing experimental and production work on the same node risks instability and is not considered production-ready.</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>Design node, Automation node, Deployer, Bundles</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>1, 2</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Dataiku Deployment Infrastructure | MUST HAVE; Dataiku Deployment Infrastructure | MUST HAVE</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
       <c r="W2" s="3" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
+      <c r="AA2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -719,62 +730,67 @@
           <t>Dataiku recommends customers stay reasonably current on DSS versions to benefit from continuous platform improvements; reviewers should identify and recommend an upgrade if appropriate, but the upgrade itself is a separate service-catalog engagement and should not be performed during the review.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Recommend upgrading DSS to a reasonably current version via a separate service engagement.</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Diagnosis shows a DSS version reasonably close to the latest generally available release.</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Diagnosis shows a DSS version many releases behind current, or a version approaching/at end-of-life.</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file lacks version information or there is no context on Dataiku's release cadence, flag needs_manual_review and recommend checking DSS release notes for the customer's version.</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Dataiku regularly enriches the platform, so staying current continuously brings value and new opportunities to customers.</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>DSS version, Upgrade</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Dataiku Version | NICE TO HAVE</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
       <c r="W3" s="3" t="n"/>
       <c r="X3" s="3" t="n"/>
       <c r="Y3" s="3" t="n"/>
       <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -807,66 +823,71 @@
           <t>DSS should run on an operating system version officially supported by Dataiku, which mainly matters for custom installs since Cloud Stacks provides a supported OS image by default; reviewers should compare the current OS against Dataiku's supported OS list and deprecation notices and recommend upgrades if needed.</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Run DSS on an operating system version officially supported by Dataiku.</t>
+        </is>
+      </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Diagnosis or accompanying metadata shows the host OS and version currently listed as supported in Dataiku's Supported Operating Systems documentation.</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>The host OS/version is deprecated or not on Dataiku's supported list for the installed DSS version.</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not capture OS name/version, flag needs_manual_review and cross-check against Dataiku's Supported Operating Systems documentation.</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Running on an unsupported OS risks instability and lack of vendor support.</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>Operating System, Custom install, Cloud Stacks</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>Operating System Version | MUST HAVE</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>The source includes an empty 'DiagParser3:' heading with no field specified underneath, so no literal parameter path could be extracted; treated as a qualitative check instead.</t>
         </is>
       </c>
-      <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -899,62 +920,67 @@
           <t>DSS should run on SSD drives rather than legacy rotational hard drives, since rotational disks can significantly degrade performance, especially on larger, multi-user instances (potentially causing a non-workable experience); reviewers should identify currently used disk types and recommend migration to SSD where feasible, noting this is typically easier on cloud than on-premise deployments.</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Run DSS on SSD storage instead of rotational hard drives for performance.</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Diagnosis or infrastructure metadata indicates SSD-backed storage underlying the DATADIR.</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Diagnosis or infrastructure metadata indicates rotational HDD storage is in use, particularly on a larger or many-user instance.</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not report the underlying disk/storage medium, flag needs_manual_review and ask the infrastructure team/customer directly.</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Rotational hard drives can severely impact performance and, on larger instances with many users, may lead to a non-workable experience.</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Disk I/O, SSD, DATADIR</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>2, 3</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Use of SSDs | MUST HAVE; Use of SSDs | MUST HAVE</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n"/>
       <c r="W5" s="3" t="n"/>
       <c r="X5" s="3" t="n"/>
       <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -989,76 +1015,81 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
+          <t>Configure a valid Spark configuration in sparkSettings wherever Spark jobs run.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; sparkSettings</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>valid spark configuration present</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>Required only if the environment executes Spark jobs; the specific parameter values shown by Dataiku are illustrative, not mandatory.</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>sparkSettings block is present and non-empty in general-settings.json, consistent with evidence of successful Spark job execution elsewhere in the diagnosis.</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>sparkSettings is missing or empty while the instance shows evidence of Spark recipes/jobs being used.</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not indicate whether Spark is used at all, flag needs_manual_review to confirm with the customer whether Spark jobs are run.</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>Without a valid Spark config, Spark jobs cannot execute at all.</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>Spark, general-settings.json, sparkSettings</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>3, 4</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>Spark runtime configurations | MUST HAVE if running spark jobs; Spark runtime configurations | MUST HAVE if running spark jobs</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U6" s="3" t="n"/>
       <c r="V6" s="3" t="n"/>
       <c r="W6" s="3" t="n"/>
       <c r="X6" s="3" t="n"/>
       <c r="Y6" s="3" t="n"/>
       <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1093,76 +1124,81 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
+          <t>Define Standard, High, Large-memory, and optional High I/O Spark configurations as a baseline.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; sparkSettings (named spark configs)</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>one_of</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Standard/High/Large-memory baseline configs, plus optional High I/O config, as documented</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Baseline reference values: Standard config \4, spspark.executor.memory=6g, spark.executor.cores=2, spark.kubernetes.memoryOverheadFactor=0.4, spark.driver.memory=1g, spark.sql.shuffle.partitions=40, spark.sql.broadcastTimeout=3600, spark.port.maxRetries=200, spark.driver.host=&lt;DSS host IP&gt;. High config - spark.executor.instances=12, spark.executor.memory=6g, spark.executor.cores=2, spark.kubernetes.memoryOverheadFactor=0.4, spark.driver.memory=1g, spark.sql.shuffle.partitions=80, spark.sql.broadcastTimeout=3600, spark.port.maxRetries=200, spark.driver.host=&lt;DSS host IP&gt;. Large memory config - spark.executor.instances=4, spark.executor.memory=12g, spark.executor.cores=2, spark.kubernetes.memoryOverheadFactor=0.6, spark.driver.memory=3g, spark.sql.shuffle.partitions=80, spark.sql.broadcastTimeout=3600, spark.port.maxRetries=200, spark.driver.host=&lt;DSS host IP&gt;. Optional High I/O config (only if there is a use case for it) - spark.executor.instances=2, spark.executor.memory=16g, spark.executor.cores=8, spark.kubernetes.memoryOverheadFactor=0.4, spark.driver.memory=3g, spark.sql.shuffle.partitions=40, spark.sql.broadcastTimeout=3600, spark.port.maxRetries=200, spark.driver.host=&lt;DSS host IP&gt;. These values are guidance, not a requirement.</t>
-        </is>
-      </c>
+      <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
+          <t>Baseline reference values: Standard config - spark.executor.instances=4, spark.executor.memory=6g, spark.executor.cores=2, spark.kubernetes.memoryOverheadFactor=0.4, spark.driver.memory=1g, spark.sql.shuffle.partitions=40, spark.sql.broadcastTimeout=3600, spark.port.maxRetries=200, spark.driver.host=&lt;DSS host IP&gt;. High config - spark.executor.instances=12, spark.executor.memory=6g, spark.executor.cores=2, spark.kubernetes.memoryOverheadFactor=0.4, spark.driver.memory=1g, spark.sql.shuffle.partitions=80, spark.sql.broadcastTimeout=3600, spark.port.maxRetries=200, spark.driver.host=&lt;DSS host IP&gt;. Large memory config - spark.executor.instances=4, spark.executor.memory=12g, spark.executor.cores=2, spark.kubernetes.memoryOverheadFactor=0.6, spark.driver.memory=3g, spark.sql.shuffle.partitions=80, spark.sql.broadcastTimeout=3600, spark.port.maxRetries=200, spark.driver.host=&lt;DSS host IP&gt;. Optional High I/O config (only if there is a use case for it) - spark.executor.instances=2, spark.executor.memory=16g, spark.executor.cores=8, spark.kubernetes.memoryOverheadFactor=0.4, spark.driver.memory=3g, spark.sql.shuffle.partitions=40, spark.sql.broadcastTimeout=3600, spark.port.maxRetries=200, spark.driver.host=&lt;DSS host IP&gt;. These values are guidance, not a requirement.</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
           <t>sparkSettings contains multiple named configs roughly matching these purposes (default/high-parallelism/large-memory, and optionally high I/O).</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Only a single undifferentiated spark config exists despite varied workload needs (e.g., both lightweight recipes and large jobs run identically).</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not list multiple sparkSettings configs or describe workload diversity, flag needs_manual_review and ask about workload variety.</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Different Spark workloads (lightweight recipes vs. large jobs vs. I/O-heavy jobs) benefit from different executor sizing and parallelism trade-offs.</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>Spark executor, Spark configuration, Kubernetes</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>4, 5</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>Define three spark configs - NICE TO HAVE; Special spark configs (only if there's use case for it)</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n"/>
       <c r="W7" s="3" t="n"/>
       <c r="X7" s="3" t="n"/>
       <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="3" t="n"/>
+      <c r="AA7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1197,76 +1233,81 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
+          <t>Use one Kubernetes namespace per user with auto-created, dynamically authenticated service accounts for Spark.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; sparkSettings (Kubernetes namespace/authentication settings)</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>one namespace per user (dss-ns-${dssUserLogin}), auto-create namespaces enabled, K8s-compliant naming, dynamic service account creation</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>No single literal diag field was given for this sub-setting; pointer is a best-effort conceptual location within sparkSettings/Kubernetes settings.</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Namespace naming pattern and auto-create/dynamic service account settings match the recommendation.</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>A single shared namespace is used for all users, or service accounts are managed manually rather than dynamically.</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not expose namespace or authentication configuration for Spark-on-Kubernetes, flag needs_manual_review.</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>Per-user namespace isolation improves security boundaries and resource tracking on Kubernetes.</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>Kubernetes namespace, Service account, Spark on Kubernetes</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>Recommended Settings NICE TO HAVE</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U8" s="3" t="n"/>
       <c r="V8" s="3" t="n"/>
       <c r="W8" s="3" t="n"/>
       <c r="X8" s="3" t="n"/>
       <c r="Y8" s="3" t="n"/>
       <c r="Z8" s="3" t="n"/>
+      <c r="AA8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1299,62 +1340,67 @@
           <t>Reviewers should functionally validate Spark execution: run a Spark-engine recipe on Kubernetes in a test project (should succeed), and separately launch a Python/R/Scala notebook with starter Spark code and run it locally (should succeed, with Spark executor pods visible in the cluster while the code runs).</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Validate Spark execution by successfully running a test Spark recipe and notebook.</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>Job/notebook execution logs show successful completion of a Spark recipe and a Spark notebook session, and cluster monitoring shows executor pods created during notebook execution.</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>The Spark recipe or notebook execution fails, hangs, or no executor pods ever appear in the cluster.</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file lacks job/notebook execution logs or cluster pod visibility, flag needs_manual_review and recommend running these test steps manually.</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>Confirms Spark integration works end-to-end, beyond just having a syntactically valid configuration.</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>Spark recipe, Spark notebook, Kubernetes executor pods</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R9" s="3" t="inlineStr">
+      <c r="S9" s="3" t="inlineStr">
         <is>
           <t>5, 6, 7</t>
         </is>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="T9" s="3" t="inlineStr">
         <is>
           <t>Additional Spark testing; Spark on Notebook MUST HAVE; Spark on Notebook MUST HAVE</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n"/>
       <c r="W9" s="3" t="n"/>
       <c r="X9" s="3" t="n"/>
       <c r="Y9" s="3" t="n"/>
       <c r="Z9" s="3" t="n"/>
+      <c r="AA9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1387,62 +1433,67 @@
           <t>Full bidirectional network connectivity between DSS and the Kubernetes/Elastic AI cluster is mandatory: workers must be able to reach Dataiku (required for Spark to start and for any container execution), and Dataiku must be able to reach workers (required for operations that bring data back to the driver, e.g. toPandas/collect/head/show/broadcast join). This should be validated by running a pySpark recipe that pulls data back to the driver and confirming success via the Main Activity Log.</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Ensure full bidirectional network connectivity between DSS and the Elastic AI cluster.</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>A pySpark recipe using collect/head/show/toPandas completes successfully, with a corresponding HEAD operation visible in the Main Activity Log, and no worker-to-DSS or DSS-to-worker connectivity errors appear in logs.</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Connection timeouts or errors between workers and the DSS host in logs, or driver-return operations failing/hanging.</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file lacks job logs or network topology details, flag needs_manual_review and recommend running the described test recipe.</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>Both directions of connectivity are mandatory prerequisites for Spark to start and for common data-return operations to work.</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>Spark driver, Spark workers, Network connectivity, Kubernetes</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>Connectivity between Dataiku and Elastic AI must be fully open MUST HAVE</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U10" s="3" t="n"/>
       <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="n"/>
       <c r="X10" s="3" t="n"/>
       <c r="Y10" s="3" t="n"/>
       <c r="Z10" s="3" t="n"/>
+      <c r="AA10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1477,76 +1528,81 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
+          <t>Configure at least one valid containerized execution config when using Elastic Compute.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; containerSettings</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>valid containerized execution configuration present</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>Required only when the customer uses Elastic Compute/Kubernetes for offloaded workloads.</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>containerSettings block is present with at least one named config with reasonable memory requests/limits.</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>containerSettings is missing or empty while the instance shows evidence of Kubernetes-based execution elsewhere in the diagnosis.</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not clarify whether Elastic Compute is used, flag needs_manual_review.</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>A valid container exec config is required to run workloads in Kubernetes.</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>Containerized execution, containerSettings, Elastic Compute</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="T11" s="3" t="inlineStr">
         <is>
           <t>Containerized execution configs | MUST HAVE if using Elastic Compute</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U11" s="3" t="n"/>
       <c r="V11" s="3" t="n"/>
       <c r="W11" s="3" t="n"/>
       <c r="X11" s="3" t="n"/>
       <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
+      <c r="AA11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1581,80 +1637,85 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
+          <t>Define Standard and Webapp container execution configs plus per-user Kubernetes namespaces.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; containerSettings (named container exec configs)</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>one_of</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>Standard config (memory request 200MB / limit 16000MB) and Webapp config (memory request 500MB / limit 500MB)</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>MB</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>Additional recommended settings: one Kubernetes namespace per user (dss-ns-${dssUserLogin}), K8s-compliant namespace names, auto-create namespaces, and virtual webapps configured to run in a container using the Webapp config.</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>containerSettings includes configs resembling the Standard and Webapp purposes with comparable memory request/limit values, and namespace settings follow a per-user pattern.</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>A single undifferentiated container config is used for both interactive workloads and webapps, or all users share one namespace.</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not list named container configs or namespace settings, flag needs_manual_review.</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>Separating configs by workload type avoids over- or under-provisioning; per-user namespaces aid isolation and cost tracking.</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>Containerized execution, Kubernetes namespace, Webapp backend</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="S12" s="3" t="inlineStr">
         <is>
           <t>8, 9</t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t>Recommendations NICE TO HAVE; Recommended Settings</t>
         </is>
       </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="n"/>
       <c r="W12" s="3" t="n"/>
       <c r="X12" s="3" t="n"/>
       <c r="Y12" s="3" t="n"/>
       <c r="Z12" s="3" t="n"/>
+      <c r="AA12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1687,62 +1748,67 @@
           <t>Reviewers should validate containerized execution end-to-end: execute a recipe in Kubernetes, launch a notebook in the cluster (pod visible in Cluster Monitoring UI), create a test webapp configured with a container backend (deployment visible in Cluster Monitoring UI), and deploy an API service to Kubernetes via the API Deployer (deployment visible in Cluster Monitoring UI and callable via sample code).</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Validate containerized execution works for recipes, notebooks, webapps, and API deployments.</t>
+        </is>
+      </c>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>Cluster monitoring evidence or reviewer test logs show successful recipe execution, a notebook pod, a webapp deployment, and an API deployment all running in Kubernetes, with the API additionally callable via sample code.</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Any of the four (recipe, notebook, webapp, API) fails to launch, or no corresponding pods/deployments ever appear in Cluster Monitoring.</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not include cluster monitoring or job execution evidence for these workload types, flag needs_manual_review and recommend running these four test steps manually.</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>Confirms containerized execution actually works for all major workload types, not merely that configuration exists.</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>Kubernetes, Recipe, Notebook, Webapp, API Deployer, Cluster Monitoring</t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="S13" s="3" t="inlineStr">
         <is>
           <t>9, 10, 11, 12</t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="T13" s="3" t="inlineStr">
         <is>
           <t>Additional container execution testing; Webapp MUST HAVE; API MUST HAVE; API MUST HAVE</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U13" s="3" t="n"/>
       <c r="V13" s="3" t="n"/>
       <c r="W13" s="3" t="n"/>
       <c r="X13" s="3" t="n"/>
       <c r="Y13" s="3" t="n"/>
       <c r="Z13" s="3" t="n"/>
+      <c r="AA13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1777,72 +1843,77 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
+          <t>Configure at least one valid Kubernetes cluster when using Elastic Compute.</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
           <t>{DATADIR}/config/clusters</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>at least one valid cluster configuration present</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>The clusters config/directory contains at least one properly defined cluster, consistent with other evidence of elastic-compute usage (spark/container jobs running on Kubernetes).</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>No cluster configuration is present despite evidence of Kubernetes-based workloads elsewhere in the diagnosis.</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not clarify whether Elastic Compute is used at all, flag needs_manual_review.</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>A valid cluster is required to offload computation to Kubernetes.</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>Cluster, Managed cluster, Unmanaged cluster, Elastic AI</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
+      <c r="R14" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R14" s="3" t="inlineStr">
+      <c r="S14" s="3" t="inlineStr">
         <is>
           <t>12, 13</t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="T14" s="3" t="inlineStr">
         <is>
           <t>Cluster configurations | MUST HAVE if using Elastic Compute; Cluster configurations | MUST HAVE if using Elastic Compute</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="n"/>
       <c r="W14" s="3" t="n"/>
       <c r="X14" s="3" t="n"/>
       <c r="Y14" s="3" t="n"/>
       <c r="Z14" s="3" t="n"/>
+      <c r="AA14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1877,76 +1948,81 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
+          <t>Use a single managed cluster with one CPU node group and autoscaling enabled.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
           <t>{DATADIR}/config/clusters (cluster topology / node group / autoscaling settings)</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>single managed cluster, one CPU node group for all standard workloads, optional GPU node group only if needed, metrics server installed, autoscaling enabled</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>No literal single field was given for this recommendation; pointer is a best-effort conceptual location within the clusters config.</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>Cluster configuration shows one managed cluster with a shared CPU node group, autoscaling enabled, metrics server installed, and a GPU node group only present when GPU workloads exist.</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>Multiple redundant clusters/node groups without clear justification, no autoscaling enabled, or a GPU node group present without any GPU workload evidence.</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not detail node groups or autoscaling settings, flag needs_manual_review.</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>Simplifies management and reduces cost while retaining elasticity for varying workloads.</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>Managed cluster, Node group, Autoscaling, Metrics server</t>
         </is>
       </c>
-      <c r="Q15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr">
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="T15" s="3" t="inlineStr">
         <is>
           <t>Recommended settings NICE TO HAVE</t>
         </is>
       </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U15" s="3" t="n"/>
       <c r="V15" s="3" t="n"/>
       <c r="W15" s="3" t="n"/>
       <c r="X15" s="3" t="n"/>
       <c r="Y15" s="3" t="n"/>
       <c r="Z15" s="3" t="n"/>
+      <c r="AA15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1981,80 +2057,85 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>Size the Kubernetes cluster appropriately for workloads, avoiding under- or over-provisioning.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; sparkSettings, general-settings.json &gt; containerSettings, general-settings.json &gt; maxRunningActivities (used to estimate cluster memory/disk sizing)</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>greater_than_or_equal</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>cluster capacity &gt;= estimated total_memory and disk needs derived from the formulas in notes</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>Illustrative sizing formulas provided by Dataiku, reproduced in full: spark_recipes_memory = global flow concurrency*spark.executor.instances*spark.executor.memory*(1+spark.kubernetes.memoryOverheadFactor) [based on the largest spark config]. spark_notebooks_memory = 30%_DSS_users*spark.executor.instances*spark.executor.memory*(1+spark.kubernetes.memoryOverheadFactor) [using associated spark config]. jupyter_notebooks_memory = 30%_DSS_users * container exec memory limit [using associated container exec config]. total_memory = spark_recipes_memory + spark_notebooks_memory + jupyter_notebooks_memory. DISK = 25GB * spark.executor.instances. Recommended instance sizing: 64 GB &lt; worker size &lt; 128 GB. These are baselines/examples; the cluster need not match this exact calculation, but must be appropriately sized for the customer's workloads based on evidence, and should not be resized without evidence of resource exhaustion.</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>Cluster memory/CPU capacity is consistent with or exceeds the estimated total_memory/disk needs given current spark/container/concurrency settings, with no signs of chronic resource exhaustion (OOM kills, pending pods) or gross over-provisioning.</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>Cluster capacity is far below estimated needs (frequent OOM kills/evictions) or drastically oversized relative to workload with no growth justification.</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file lacks cluster capacity metrics or the underlying spark/container/concurrency settings needed to compute the estimate, flag needs_manual_review and recommend gathering these values.</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>Prevents both instability/performance degradation from under-sizing and cost waste from over-sizing.</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>Cluster sizing, Spark executor memory, Container exec memory limit, maxRunningActivities, Global flow concurrency</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R16" s="3" t="inlineStr">
+      <c r="S16" s="3" t="inlineStr">
         <is>
           <t>14, 15</t>
         </is>
       </c>
-      <c r="S16" s="3" t="inlineStr">
+      <c r="T16" s="3" t="inlineStr">
         <is>
           <t>Cluster sizing | MUST HAVE; Cluster sizing | MUST HAVE</t>
         </is>
       </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="U16" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U16" s="3" t="n"/>
       <c r="V16" s="3" t="n"/>
       <c r="W16" s="3" t="n"/>
       <c r="X16" s="3" t="n"/>
       <c r="Y16" s="3" t="n"/>
       <c r="Z16" s="3" t="n"/>
+      <c r="AA16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2089,72 +2170,77 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>Set a global default cluster and execution config with proper resource limits when offloading broadly.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; defaultK8sClusterId and general-settings.json &gt; defaultExecutionConfig</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>both set to valid, non-resource-hogging values when Elastic AI/offloading is used broadly</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>Both defaultK8sClusterId and defaultExecutionConfig are set to valid values, and the referenced execution config has reasonable memory/CPU requests and limits.</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>These fields are unset despite most recipes being offloaded to Kubernetes, or the default execution config lacks resource limits/requests (resource-hogging risk).</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not clarify the proportion of recipes offloaded to Kubernetes, flag needs_manual_review to confirm intended usage pattern with the customer.</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>Setting a global default simplifies configuration management and avoids inconsistent per-recipe settings; an unset or misconfigured default risks uncontrolled resource usage.</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>defaultK8sClusterId, defaultExecutionConfig, Containerized execution, Elastic AI</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R17" s="3" t="inlineStr">
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t>15, 16</t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="T17" s="3" t="inlineStr">
         <is>
           <t>Default Cluster &amp; Default Containerized Execution Config | MUST HAVE if Elastic AI is used; Default Cluster &amp; Default Containerized Execution Config | MUST HAVE if Elastic AI is used</t>
         </is>
       </c>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U17" s="3" t="n"/>
       <c r="V17" s="3" t="n"/>
       <c r="W17" s="3" t="n"/>
       <c r="X17" s="3" t="n"/>
       <c r="Y17" s="3" t="n"/>
       <c r="Z17" s="3" t="n"/>
+      <c r="AA17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -2189,72 +2275,77 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
+          <t>Enable CDE and build its base image to offload visual recipes to Kubernetes.</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; cdeEnabled and general-settings.json &gt; defaultExecutionConfigForVisualRecipesWorkloads</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>cdeEnabled=true and defaultExecutionConfigForVisualRecipesWorkloads set to a valid execution config</t>
         </is>
       </c>
-      <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>cdeEnabled is true, base CDE image build evidence exists, defaultExecutionConfigForVisualRecipesWorkloads is set, and a sample visual recipe shows Engine: DSS (containerized).</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>cdeEnabled is false or unset while the customer relies on Kubernetes offloading for visual recipes, or a visual recipe fails to show the containerized engine.</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not indicate whether visual recipe offloading to Kubernetes is desired, flag needs_manual_review.</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="P18" s="3" t="inlineStr">
         <is>
           <t>Ensures visual recipes can actually be executed on the cluster with an appropriate base image and default resource config.</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>CDE, cdeEnabled, Visual recipes, Containerized execution</t>
         </is>
       </c>
-      <c r="Q18" s="3" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>architecture_compute_cost</t>
         </is>
       </c>
-      <c r="R18" s="3" t="inlineStr">
+      <c r="S18" s="3" t="inlineStr">
         <is>
           <t>16, 17, 18</t>
         </is>
       </c>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="T18" s="3" t="inlineStr">
         <is>
           <t>Containerized Visual Recipes (CDE) | NICE TO HAVE; Containerized Visual Recipes (CDE) | NICE TO HAVE; Containerized Visual Recipes (CDE) | NICE TO HAVE</t>
         </is>
       </c>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="U18" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U18" s="3" t="n"/>
       <c r="V18" s="3" t="n"/>
       <c r="W18" s="3" t="n"/>
       <c r="X18" s="3" t="n"/>
       <c r="Y18" s="3" t="n"/>
       <c r="Z18" s="3" t="n"/>
+      <c r="AA18" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2267,7 +2358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2276,26 +2367,27 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
     <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2331,100 +2423,105 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>statement_short</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>parameter_hint</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>operator</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>expected_value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>expected_condition_notes</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>supporting_evidence</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>contradicting_evidence</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>insufficient_evidence_handling</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rationale</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dataiku_concepts</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>source_document</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>source_page</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ambiguity_notes</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>validation_status</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>evidence_found</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>validated_by</t>
         </is>
@@ -2461,66 +2558,71 @@
           <t>For an established platform, confirm that each node's instance ID (found in {DATA_DIR}/install.ini) is accurately recorded in the platform's tracking/tooling system.</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Confirm each node's instance ID is accurately recorded in platform tracking tooling.</t>
+        </is>
+      </c>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Platform tooling/documentation shows an instance ID for each node matching the value found in {DATA_DIR}/install.ini on that node.</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Instance IDs are missing, blank, or mismatched between install.ini and the platform tooling records.</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>A diagnosis file alone can show the instance ID value in install.ini but cannot confirm whether it is accurately recorded in external platform tooling; flag as needs_manual_review to cross-check against the tooling record.</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>Accurate instance ID records ensure the platform tooling correctly tracks and manages each node.</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>install.ini, instance tracking</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>security_permissions_compliance</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>1, 2</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Verify/Capture Instance IDs | NICE TO HAVE; DiagParser3</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>No literal JSON field/diag pointer given beyond the file path itself; this is more a documentation-accuracy check than a technical setting.</t>
         </is>
       </c>
-      <c r="V2" s="3" t="n"/>
       <c r="W2" s="3" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
+      <c r="AA2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2555,72 +2657,77 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>Enable User Isolation Framework with impersonation rules mapping all users away from the service account.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>{DATA_DIR}/config/general-settings.json &gt; impersonation.enabled</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>general-settings.json shows impersonation.enabled: true with userRules configured as a one-to-one mapping or regex rule mapping DSS users to non-service-account identities; no Sanity Check warnings about UIF; for K8s workloads a per-user namespace strategy is evident; for Hadoop workloads Sentry/Ranger integration is present.</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>impersonation.enabled is false or absent, userRules are missing/overly permissive (e.g., mapping to the dataiku service account), Sanity Check warnings reference UIF, or Kubernetes/Hadoop workloads lack namespace-per-user/Sentry-Ranger controls.</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file lacks general-settings.json impersonation details or workload-specific config, flag as needs_manual_review, noting that longstanding instances without UIF require careful, considerate customer messaging and that disabling/downgrading UIF is not supported.</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>UIF and correct impersonation rules are required for proper user isolation and security; without them workloads may run under a shared service account, creating security risk and instability in multi-user environments.</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>User Isolation Framework, impersonation, Kubernetes namespaces, Hadoop Sentry/Ranger</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>security_permissions_compliance</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>2, 3</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>User Isolation Framework | MUST HAVE; User Isolation Framework | MUST HAVE (Front End/Back End/Notes)</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
       <c r="W3" s="3" t="n"/>
       <c r="X3" s="3" t="n"/>
       <c r="Y3" s="3" t="n"/>
       <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2655,76 +2762,81 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>Add DSS-controlled cgroup hierarchies to additional_allowed_file_dirs in security-config.ini under UIF.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>/etc/dataiku-security/INSTALL_ID/security-config.ini &gt; [dirs] &gt; additional_allowed_file_dirs</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>DSS-controlled cgroup hierarchy paths listed</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Literal file path and key given in source; exact expected paths are environment-specific so only existence/inclusion can be checked.</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>security-config.ini shows additional_allowed_file_dirs under [dirs] populated with the cgroup hierarchy paths under DSS control.</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>additional_allowed_file_dirs is missing or does not include the relevant cgroup hierarchy paths despite cgroups being enabled under UIF.</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>If security-config.ini is not present in the diagnosis bundle, flag as needs_manual_review since this file is typically outside standard diagnostic exports.</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Proper directory allowlisting ensures DSS-managed cgroup hierarchies function correctly under user isolation.</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>cgroups, security-config.ini, User Isolation Framework</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>security_permissions_compliance</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>User Isolation Framework | MUST HAVE (Back End)</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -2759,76 +2871,81 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>Enable cgroups with a memory limit sized per the recommended heuristic for instance RAM.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>{DATA_DIR}/config/general-settings.json &gt; cgroupSettings.enabled</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Additional checks required: cgroupSettings &gt; cgroups memory limit target should be set and sized per the documented heuristic (approx. 50-75% of physical memory depending on total RAM); no single literal field given for the limit value itself, so compare against the formula in evaluation_guidance.</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>general-settings.json shows cgroupSettings.enabled: true, targets set for each category under cgroups, and a memory limit configured on memory cgroups (e.g., memory/DSS) that approximates the documented formula based on total instance memory (e.g., ~75% for &gt;120GB, ~66% for 60-120GB, total-20GB for 30-60GB, ~50% below 30GB). Front-end equivalent: Administration &gt; Settings &gt; Resource Control &gt; cgroups shows 'Enable cgroups support' selected with placements and memory limits configured.</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>cgroupSettings.enabled is false/absent, no memory limit is set on memory cgroups, or the configured limit is far below the heuristic (e.g., unlimited or near-total memory), risking instability.</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>If cgroupSettings or category placements are not visible in the diagnosis file, flag as needs_manual_review; also check whether the instance was recently reprovisioned (Cloud Stacks) or upgraded, as cgroup limits/placements may not auto-update and new placements may need to be added post-upgrade.</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>A memory cgroup limit prevents runaway processes from destabilizing or degrading the DSS instance; sizing per the heuristic balances safety with usable memory.</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>cgroups, memory limits, Resource Control</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>security_permissions_compliance</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>3, 4, 5</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>CGroups | MUST HAVE; CGroups | MUST HAVE (Review steps); CGroups | MUST HAVE (Notes)</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n"/>
       <c r="W5" s="3" t="n"/>
       <c r="X5" s="3" t="n"/>
       <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2863,80 +2980,85 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
+          <t>Avoid setting JEK-specific cgroup limits except in rare specialized edge cases.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; cgroupSettings (JEK-specific cgroup entries)</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>not_exists</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>No JEK-specific cgroup limits configured</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>No literal field path given for JEK-specific cgroup entries; conceptual pointer based on general cgroupSettings structure.</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>cgroupSettings configuration shows no per-JEK-specific memory/CPU limits distinct from the general DSS cgroup limits.</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Specific cgroup limits are found configured for individual Job Kernels without documented justification for a specialized edge case.</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not clearly break down cgroup settings by JEK vs. general placement, flag as needs_manual_review and recommend checking internal deep-dive documentation if an exception is suspected.</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>Per-JEK cgroup limits can cause unexpected execution throttling, degrading job performance.</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>cgroups, Job Execution Kernel (JEK)</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>security_permissions_compliance</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>CGroups | MUST HAVE</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>Priority classification is inferred; this could arguably be nice_to_have as it's a caution rather than a baseline requirement, but the explicit performance-degradation risk supports must_have.</t>
         </is>
       </c>
-      <c r="V6" s="3" t="n"/>
       <c r="W6" s="3" t="n"/>
       <c r="X6" s="3" t="n"/>
       <c r="Y6" s="3" t="n"/>
       <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2971,76 +3093,81 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
+          <t>Verify HTTPS access to DSS is configured natively or via a reverse proxy.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
           <t>install.ini &gt; [server] section (HTTPS settings) or /data/dataiku/dss_data/run/nodes-directory.json</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>HTTPS enabled (natively or via reverse proxy)</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>No single literal key name given for the HTTPS flag itself; pointer is to the file/section where it should be inspected.</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>install.ini [server] section shows native HTTPS parameters configured, or nodes-directory.json shows HTTPS URLs/ports for nodes, or customer confirms a reverse proxy terminates HTTPS in front of DSS.</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Only HTTP is configured with no reverse proxy in front, and install.ini/nodes-directory.json show no HTTPS-related configuration.</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file does not include install.ini or nodes-directory.json content, or if reverse-proxy setup is external to DSS, flag as needs_manual_review and confirm directly with the customer.</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>HTTPS protects data in transit and is recommended practice for securing access to DSS.</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>HTTPS, reverse proxy, install.ini, nodes-directory.json</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>security_permissions_compliance</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>5, 6</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>HTTPS | NICE TO HAVE; HTTPS | NICE TO HAVE (Review steps)</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n"/>
       <c r="W7" s="3" t="n"/>
       <c r="X7" s="3" t="n"/>
       <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="3" t="n"/>
+      <c r="AA7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -3055,84 +3182,105 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>qualitative_practice</t>
+          <t>specific_setting</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Security Model &amp; Groups</t>
+          <t>Secure Cookies &amp; Transport Security</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>DSS Groups Security Model Appropriately Defined</t>
+          <t>Secure Cookies Enabled (security.secureCookies)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Confirm the client has an appropriate set of groups within their DSS security model: that they understand the DSS security model, that appropriate groups have been defined, and that permissions are properly granted based on those groups.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
+          <t>By default, DSS login cookies lack the Secure flag and could be sent over unencrypted HTTP. Where DSS is served entirely over HTTPS (natively or via reverse proxy), set security.secureCookies to true in general-settings.json so session cookies are only transmitted over secure connections, enhancing session security.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Enable secure cookies (security.secureCookies=true) once DSS is served entirely over HTTPS.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>general-settings.json &gt; security.secureCookies</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>equals</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Documentation or discussion notes indicate the customer has defined distinct DSS groups aligned to roles/functions, with permissions (project access, connections, etc.) granted based on group membership rather than ad hoc per-user grants.</t>
+          <t>Should only be enabled once DSS is served exclusively over HTTPS everywhere (natively or via reverse proxy); enabling without full HTTPS coverage would break login for HTTP-only clients.</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Evidence of a flat or minimal group structure, permissions granted broadly or per-individual-user without group-based structure, or customer confusion about the security model in review notes.</t>
+          <t>general-settings.json shows security.secureCookies: true, and HTTPS is confirmed enabled for all users (natively or via reverse proxy).</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>A diagnosis file typically cannot show group design intent or customer understanding; flag as needs_manual_review and recommend a discussion with the client to assess this.</t>
+          <t>secureCookies is false or absent while HTTPS is used for all users, meaning session cookies could still be sent over unencrypted connections.</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>A well-structured group model ensures permissions are manageable, auditable, and scalable as the platform grows.</t>
+          <t>If HTTPS usage status or the security section of general-settings.json is not visible in the diagnosis file, flag as needs_manual_review.</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>DSS groups, security model, permissions</t>
+          <t>Secure cookies prevent cookies from being transmitted over unencrypted connections, reducing session hijacking risk when HTTPS is in use; by default DSS cookies lack the Secure flag, exposing them to transmission over HTTP absent this setting.</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>security_permissions_compliance</t>
+          <t>secure cookies, general-settings.json, security, HTTPS</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>advanced_security_options, security_permissions_compliance</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>DSS groups security model | NICE TO HAVE</t>
+          <t>6, 7, 2, 3</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
+          <t>Secure Cookies | NICE TO HAVE; Secure Cookies | NICE TO HAVE (Review steps); Using secure cookies; Using secure cookies</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>Entirely a qualitative, discussion-based check with no technical pointer.</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="n"/>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Source documents disagree on priority: the Security &amp; Permissions review guide explicitly tags this as NICE TO HAVE, while the Advanced Security Options documentation implies a MUST HAVE classification via inferred reasoning about session hardening. The explicit source designation (nice_to_have) was retained per merge precedence rules.</t>
+        </is>
+      </c>
       <c r="W8" s="3" t="n"/>
       <c r="X8" s="3" t="n"/>
       <c r="Y8" s="3" t="n"/>
       <c r="Z8" s="3" t="n"/>
+      <c r="AA8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3147,96 +3295,89 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>specific_setting</t>
+          <t>qualitative_practice</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>LDAP Configuration</t>
+          <t>Security Model &amp; Groups</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>LDAP Authorized Groups Configured</t>
+          <t>DSS Groups Security Model Appropriately Defined</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Where DSS is integrated with LDAP, ensure Authorized Groups are configured so that only members of specified groups can connect; if LDAP is enabled but no Authorized Groups are set, all LDAP users matching the User filter query can connect, which should be flagged to the customer as a recommended improvement.</t>
+          <t>Confirm the client has an appropriate set of groups within their DSS security model: that they understand the DSS security model, that appropriate groups have been defined, and that permissions are properly granted based on those groups.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>{DATA_DIR}/config/general-settings.json &gt; ldapSettings.authorizedGroups</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>exists</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>non-empty (populated with one or more groups)</t>
-        </is>
-      </c>
+          <t>Confirm DSS groups are well-defined and permissions are granted based on group membership.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Check is conditional on ldapSettings.enabled being true.</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>general-settings.json shows ldapSettings.enabled: true and authorizedGroups populated with one or more group entries; front-end equivalent shows Authorized groups field populated under Login (LDAP, SSO) &amp; Security &gt; Groups mapping.</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>ldapSettings.enabled is true but authorizedGroups is empty or absent, meaning all LDAP users passing the User filter can connect without group-based restriction.</t>
+          <t>Documentation or discussion notes indicate the customer has defined distinct DSS groups aligned to roles/functions, with permissions (project access, connections, etc.) granted based on group membership rather than ad hoc per-user grants.</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>If ldapSettings is not present or LDAP is not enabled, this check does not apply; if enabled but authorizedGroups status is unclear, flag as needs_manual_review.</t>
+          <t>Evidence of a flat or minimal group structure, permissions granted broadly or per-individual-user without group-based structure, or customer confusion about the security model in review notes.</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Authorized Groups restrict which LDAP-authenticated users may connect to DSS, reducing unauthorized access risk.</t>
+          <t>A diagnosis file typically cannot show group design intent or customer understanding; flag as needs_manual_review and recommend a discussion with the client to assess this.</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>LDAP, authorizedGroups, authentication</t>
+          <t>A well-structured group model ensures permissions are manageable, auditable, and scalable as the platform grows.</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
+          <t>DSS groups, security model, permissions</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
           <t>security_permissions_compliance</t>
         </is>
       </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>7, 8</t>
-        </is>
-      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>LDAP: Authorized groups | NICE TO HAVE; LDAP: Authorized groups | NICE TO HAVE (Review steps)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="n"/>
-      <c r="V9" s="3" t="n"/>
+          <t>DSS groups security model | NICE TO HAVE</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>Entirely a qualitative, discussion-based check with no technical pointer.</t>
+        </is>
+      </c>
       <c r="W9" s="3" t="n"/>
       <c r="X9" s="3" t="n"/>
       <c r="Y9" s="3" t="n"/>
       <c r="Z9" s="3" t="n"/>
+      <c r="AA9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3251,77 +3392,93 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>qualitative_practice</t>
+          <t>specific_setting</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Single Sign-On</t>
+          <t>LDAP Configuration</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>SSO Enablement Reviewed</t>
+          <t>LDAP Authorized Groups Configured</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Verify whether SSO is enabled for the DSS instance; if not, discuss with the customer whether enabling SSO would benefit their deployment.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
+          <t>Where DSS is integrated with LDAP, ensure Authorized Groups are configured so that only members of specified groups can connect; if LDAP is enabled but no Authorized Groups are set, all LDAP users matching the User filter query can connect, which should be flagged to the customer as a recommended improvement.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Configure LDAP Authorized Groups to restrict which LDAP users can connect to DSS.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>{DATA_DIR}/config/general-settings.json &gt; ldapSettings.authorizedGroups</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>exists</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>non-empty (populated with one or more groups)</t>
+        </is>
+      </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Configuration or documentation indicates SSO is enabled and integrated with the customer's identity provider.</t>
+          <t>Check is conditional on ldapSettings.enabled being true.</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>SSO is not configured and there is no record of a discussion with the customer about its potential benefits.</t>
+          <t>general-settings.json shows ldapSettings.enabled: true and authorizedGroups populated with one or more group entries; front-end equivalent shows Authorized groups field populated under Login (LDAP, SSO) &amp; Security &gt; Groups mapping.</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>Diagnosis files may not clearly expose SSO configuration; if unclear, flag as needs_manual_review and recommend confirming SSO status directly with the customer/admin settings.</t>
+          <t>ldapSettings.enabled is true but authorizedGroups is empty or absent, meaning all LDAP users passing the User filter can connect without group-based restriction.</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>SSO can improve authentication security and user experience by centralizing identity management.</t>
+          <t>If ldapSettings is not present or LDAP is not enabled, this check does not apply; if enabled but authorizedGroups status is unclear, flag as needs_manual_review.</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>SSO, authentication</t>
+          <t>Authorized Groups restrict which LDAP-authenticated users may connect to DSS, reducing unauthorized access risk.</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
+          <t>LDAP, authorizedGroups, authentication</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
           <t>security_permissions_compliance</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>SSO | NICE TO HAVE</t>
+          <t>7, 8</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>LDAP: Authorized groups | NICE TO HAVE; LDAP: Authorized groups | NICE TO HAVE (Review steps)</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>No literal field path or diag pointer is given for SSO status in this document.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="V10" s="3" t="n"/>
@@ -3329,6 +3486,7 @@
       <c r="X10" s="3" t="n"/>
       <c r="Y10" s="3" t="n"/>
       <c r="Z10" s="3" t="n"/>
+      <c r="AA10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3348,79 +3506,181 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Proxy Configuration</t>
+          <t>Single Sign-On</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Proxy Configuration Reviewed and Documented</t>
+          <t>SSO Enablement Reviewed</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Take the opportunity to review and understand any proxy configuration in use, ensuring it is accurately documented in the platform tooling.</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
+          <t>Verify whether SSO is enabled for the DSS instance; if not, discuss with the customer whether enabling SSO would benefit their deployment.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Verify whether SSO is enabled and discuss potential benefits with the customer.</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Platform tooling/documentation contains accurate, up-to-date proxy configuration details matching the instance's actual proxy setup.</t>
-        </is>
-      </c>
+      <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Proxy configuration is undocumented, outdated, or inconsistent with the actual instance setup.</t>
+          <t>Configuration or documentation indicates SSO is enabled and integrated with the customer's identity provider.</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>A diagnosis file is unlikely to fully capture proxy configuration or the state of external documentation; flag as needs_manual_review to confirm with the customer and platform tooling records.</t>
+          <t>SSO is not configured and there is no record of a discussion with the customer about its potential benefits.</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Understanding and documenting proxy configuration helps ensure connectivity and troubleshooting information is accurate and available.</t>
+          <t>Diagnosis files may not clearly expose SSO configuration; if unclear, flag as needs_manual_review and recommend confirming SSO status directly with the customer/admin settings.</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>proxy configuration, platform tooling</t>
+          <t>SSO can improve authentication security and user experience by centralizing identity management.</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
+          <t>SSO, authentication</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
           <t>security_permissions_compliance</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>Proxy configuration | NICE TO HAVE</t>
-        </is>
-      </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
+          <t>SSO | NICE TO HAVE</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>No technical pointer given; purely a documentation/understanding check.</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="n"/>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>No literal field path or diag pointer is given for SSO status in this document.</t>
+        </is>
+      </c>
       <c r="W11" s="3" t="n"/>
       <c r="X11" s="3" t="n"/>
       <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
+      <c r="AA11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>SEC-011</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>nice_to_have</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>qualitative_practice</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Proxy Configuration</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Proxy Configuration Reviewed and Documented</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Take the opportunity to review and understand any proxy configuration in use, ensuring it is accurately documented in the platform tooling.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Review and accurately document any proxy configuration in the platform tooling.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Platform tooling/documentation contains accurate, up-to-date proxy configuration details matching the instance's actual proxy setup.</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Proxy configuration is undocumented, outdated, or inconsistent with the actual instance setup.</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>A diagnosis file is unlikely to fully capture proxy configuration or the state of external documentation; flag as needs_manual_review to confirm with the customer and platform tooling records.</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Understanding and documenting proxy configuration helps ensure connectivity and troubleshooting information is accurate and available.</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>proxy configuration, platform tooling</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>security_permissions_compliance</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>Proxy configuration | NICE TO HAVE</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>No technical pointer given; purely a documentation/understanding check.</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="n"/>
+      <c r="X12" s="3" t="n"/>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="3" t="n"/>
+      <c r="AA12" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3433,7 +3693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3442,26 +3702,27 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
     <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3497,100 +3758,105 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>statement_short</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>parameter_hint</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>operator</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>expected_value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>expected_condition_notes</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>supporting_evidence</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>contradicting_evidence</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>insufficient_evidence_handling</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rationale</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dataiku_concepts</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>source_document</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>source_page</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ambiguity_notes</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>validation_status</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>evidence_found</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>validated_by</t>
         </is>
@@ -3629,76 +3895,81 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>Use internal code environments as default for RAG, document extraction, and PII detection.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; generativeAISettings &gt; defaultRetrievableKnowledgeCodeEnv</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>not_exists</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>absent (i.e., using internal default code-env, containerMode NONE)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>If defaultRetrievableKnowledgeCodeEnv is present with a custom value and containerMode is INHERIT, a non-internal code-env is in use. Also check presidioBasedPIIDetection (PII detection) and embedDocumentsRecipeSettings (document extraction) keys for equivalent non-internal overrides.</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>general-settings.json generativeAISettings shows containerMode NONE with no defaultRetrievableKnowledgeCodeEnv key, and PII/doc extraction sections show no custom code-env overrides; Admin &gt; Code-envs &gt; Internal envs shows RAG/PII/Doc extraction set up as internal.</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>defaultRetrievableKnowledgeCodeEnv key present with a non-internal value, containerMode INHERIT, or a warning banner shown in Admin &gt; Settings &gt; Other &gt; LLM Mesh / Code-envs &gt; Internal envs.</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>If generativeAISettings section is absent from the diagnosis, flag needs_manual_review to check the UI directly.</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>Internal code envs bundle the correct/supported dependencies (e.g., libreoffice for document extraction); using a non-internal env can cause missing dependencies or unsupported behavior.</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>LLM Mesh, code environments, RAG, PII detection, document extraction</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>generative_ai_acceleration</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>1, 2, 3</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>LLM Mesh and Agents MUST HAVE:; RAG, Doc extraction, PII detection; Instance Diags / DiagParser3</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
       <c r="W2" s="3" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
+      <c r="AA2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3733,80 +4004,85 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>Install the Hugging Face code env and verify GPU cluster prerequisites when used.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>Administration &gt; Code-envs &gt; INTERNAL_huggingface_local_v1 (installed)</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>installed and configured</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>No literal diag JSON field was given in the source for this check; infrastructure prerequisites (GPU compute capability, CUDA/driver version, Python 3.11, Almalinux 9) are not verifiable from a diagnosis JSON alone and require manual/infra review.</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Code-env listing shows INTERNAL_huggingface_local_v1 present and in use; Elastic AI cluster configuration references GPU-enabled nodes.</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Env missing, or Hugging Face local LLM feature is referenced in use without a corresponding GPU-enabled Elastic AI cluster.</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis doesn't reference Hugging Face local LLM usage, treat as not applicable; if usage is confirmed elsewhere but infra details aren't in the diagnosis, flag needs_manual_review.</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Without the correct GPU cluster, driver/CUDA compatibility, base image, and Python version, local Hugging Face LLMs will not function.</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Hugging Face, Elastic AI, Kubernetes, GPU, code environments</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>generative_ai_acceleration</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Hugging face local LLMs (only if applicable)</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>Conditional feature ('only if applicable'); priority applies only when the customer has opted to use this capability.</t>
         </is>
       </c>
-      <c r="V3" s="3" t="n"/>
       <c r="W3" s="3" t="n"/>
       <c r="X3" s="3" t="n"/>
       <c r="Y3" s="3" t="n"/>
       <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3841,72 +4117,77 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>Set a default project and webapp for Trace Explorer so view traces works.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; llmTraceSettings.traceExplorerDefaultWebApp</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>projectKey and webAppId both set to non-empty values</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>llmTraceSettings.traceExplorerDefaultWebApp present in general-settings.json with non-empty projectKey and webAppId fields.</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>llmTraceSettings missing entirely, or traceExplorerDefaultWebApp present but empty/null.</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>If general-settings.json content isn't captured in the diagnosis, flag needs_manual_review to verify via the UI.</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Without this default configuration, the trace-viewing shortcut from Prompt Studio/Agents/RAG LLMs will not function.</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>Trace Explorer, LLM Mesh, Agents</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>generative_ai_acceleration</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>3, 4</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>Trace Explorer MUST HAVE:; Instance Diags / DiagParser3</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3941,72 +4222,77 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>Confirm AI Services Terms of Use are accepted and AI Services are enabled.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; dataikuAIServicesTermsOfUseAccepted / enabled</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Also check byoTermsOfUseAccepted for Bring-your-own-LLM mode. Internet whitelisting of ai-gateway.api-services.dataiku.io is not verifiable from diagnosis JSON alone.</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>general-settings.json shows dataikuAIServicesTermsOfUseAccepted=true and enabled=true.</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>enabled=false or Terms of Use not accepted while AI Services usage is expected/observed.</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>If AI Services keys are absent from the diagnosis, treat as not enabled and flag needs_manual_review to confirm with the customer whether AI Services usage is intended.</t>
         </is>
       </c>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>AI Services, Terms of Use, LLM Mesh</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>generative_ai_acceleration</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>4, 5</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>AI Services NICE TO HAVE:; Instance Diags / DiagParser3</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n"/>
       <c r="W5" s="3" t="n"/>
       <c r="X5" s="3" t="n"/>
       <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -4041,68 +4327,73 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
+          <t>Set a Reference project key and main LLM model when using Bring Your Own LLM.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; localAIServerSettings.referenceProjectKey / mainLLMId</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>non-empty values set for both fields</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>localAIServerSettings.useLocalServer=true with referenceProjectKey and mainLLMId populated (e.g., 'openai:openai-adrissi:gpt-5.5').</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>useLocalServer=true but referenceProjectKey or mainLLMId missing or empty.</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>If localAIServerSettings is absent from the diagnosis, flag needs_manual_review to confirm whether Bring Your Own LLM mode is in use.</t>
         </is>
       </c>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>Bring Your Own LLM, AI Services, LLM Mesh</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>generative_ai_acceleration</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>5, 6</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>Bring your own LLM Mode; Instance Diags / DiagParser3</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U6" s="3" t="n"/>
       <c r="V6" s="3" t="n"/>
       <c r="W6" s="3" t="n"/>
       <c r="X6" s="3" t="n"/>
       <c r="Y6" s="3" t="n"/>
       <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -4137,76 +4428,81 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
+          <t>Use at least ChatGPT 5.2 for Bring Your Own LLM; avoid version 5.1.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; localAIServerSettings.mainLLMId (and responseFormatAwareLLMId/fastLightLLMId)</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>not_equals</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>ChatGPT 5.1 or earlier / unsupported model versions</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Exact version comparison against the recommended minimum (ChatGPT 5.2) may require manual judgment; refer to https://doc.dataiku.com/dss/latest/ai-assistants/setup.html#bring-your-own-llm-mode.</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>mainLLMId/related LLM IDs reference gpt-5.2 or later.</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>mainLLMId/related LLM IDs reference gpt-5.1 or an older/unsupported model.</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>If the model identifier is ambiguous, non-OpenAI, or version cannot be determined, flag needs_manual_review and reference the setup documentation.</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Using unsupported model versions is stated to produce poor results.</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>Bring Your Own LLM, Model selection, AI Assistants</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>generative_ai_acceleration</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>6, 7</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>Bring your own LLM Mode; Bring your own LLM Mode</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n"/>
       <c r="W7" s="3" t="n"/>
       <c r="X7" s="3" t="n"/>
       <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="3" t="n"/>
+      <c r="AA7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -4241,68 +4537,73 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
+          <t>Configure default embedding, LLM, and image-generation models for Cobuild agent building.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; aiDrivenAnalyticsSettings.agentBuildingSettings.{defaultEmbeddingLLMId, defaultLLMId, defaultImageGenerationLLMId}</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>exists</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>all three fields populated with valid LLM IDs</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>agentBuildingSettings block shows non-empty defaultEmbeddingLLMId, defaultLLMId, and defaultImageGenerationLLMId values.</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>One or more of these fields is missing or empty while Cobuild/AI Assistants is enabled.</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>If aiDrivenAnalyticsSettings is absent from the diagnosis, flag needs_manual_review to confirm whether Cobuild/AI Assistants is enabled for this customer.</t>
         </is>
       </c>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>Cobuild, AI Assistants, Agent building</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>generative_ai_acceleration</t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>7, 8, 9</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>Cobuild; Cobuild; Instance Diags / DiagParser3</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U8" s="3" t="n"/>
       <c r="V8" s="3" t="n"/>
       <c r="W8" s="3" t="n"/>
       <c r="X8" s="3" t="n"/>
       <c r="Y8" s="3" t="n"/>
       <c r="Z8" s="3" t="n"/>
+      <c r="AA8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -4335,66 +4636,71 @@
           <t>To access AI Assistant Logs (ui.json, runtime.json, traces per project) in an Instance Diagnostic (V14.7+), an administrator must explicitly select the option to include these logs when generating a diagnostic via Administration &gt; Maintenance &gt; Instance Diagnostic.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Select the option to include AI Assistant debug logs when generating instance diagnostics.</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>The diagnostic bundle includes an 'AI Assistants debug data' section organized by project with ui.json, runtime.json, and traces files.</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>Diagnostic bundle lacks these files despite AI Assistants being actively used on the instance.</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>If the diagnostic was generated on a version prior to 14.7, or the inclusion option's state can't be determined, flag needs_manual_review and note reviewers should confirm the option was selected during diagnostic generation.</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>Without selecting this option, AI Assistant logs are not captured, limiting the reviewer's ability to diagnose LLM Mesh/agent-building issues.</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>Instance Diagnostic, AI Assistants, Logging</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>generative_ai_acceleration</t>
         </is>
       </c>
-      <c r="R9" s="3" t="inlineStr">
+      <c r="S9" s="3" t="inlineStr">
         <is>
           <t>9, 10</t>
         </is>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="T9" s="3" t="inlineStr">
         <is>
           <t>Instance Diags / DiagParser3; Instance Diags / DiagParser3</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="V9" s="3" t="inlineStr">
         <is>
           <t>This is more a diagnostic-generation process note than a platform configuration state, so evaluability from a static diagnosis file is limited.</t>
         </is>
       </c>
-      <c r="V9" s="3" t="n"/>
       <c r="W9" s="3" t="n"/>
       <c r="X9" s="3" t="n"/>
       <c r="Y9" s="3" t="n"/>
       <c r="Z9" s="3" t="n"/>
+      <c r="AA9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -4427,66 +4733,71 @@
           <t>Before a user can deploy an Agent Hub instance, they must have permissions for writing project content in the hosting project, writing isolated code execution, WebApp impersonation, and (if Quick agents are enabled) create projects; alternatively the user could be a DSS administrator, though a dedicated service account is preferred.</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Grant Agent Hub deployers write project content, isolated code execution, and webapp impersonation permissions.</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>Administration &gt; Security &gt; Groups shows the Agent Hub deployer's group granted 'Write project content', 'Write isolated code execution', and 'WebApp impersonation' permissions (plus 'Create projects' if Quick agents are enabled), or the deployer is a DSS admin/service account.</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>The deployer's group lacks one or more of these permissions and is not an admin/service account, or logs show 'Not authorized' errors when creating the Agent Hub WebApp.</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis file lacks per-user/group permission detail, flag needs_manual_review and recommend checking Administration &gt; Security &gt; Groups directly.</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>Missing permissions cause deployment failures such as 'Not authorized' errors when creating the Agent Hub WebApp.</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>Agent Hub, Permissions, Groups, WebApp</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>generative_ai_acceleration</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t>10, 11, 12</t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>Agent Hub NICE TO HAVE:; Writing isolated code execution; WebApp impersonation</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="V10" s="3" t="inlineStr">
         <is>
           <t>Although the parent topic is tagged NICE TO HAVE, the described permission requirements are phrased as mandatory ('must have permissions') for successful deployment; classification follows the explicit heading tag.</t>
         </is>
       </c>
-      <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="n"/>
       <c r="X10" s="3" t="n"/>
       <c r="Y10" s="3" t="n"/>
       <c r="Z10" s="3" t="n"/>
+      <c r="AA10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4519,62 +4830,67 @@
           <t>Dataiku recommends using a dedicated service account rather than an instance administrator account to manage and configure an Agent Hub instance.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Use a dedicated service account rather than an admin account to manage Agent Hub.</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>Agent Hub is managed/configured by a dedicated service account (non-admin) holding the specific required permissions rather than by a full instance administrator.</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>Agent Hub is managed exclusively using a full instance administrator account.</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis doesn't identify the account type managing Agent Hub, flag needs_manual_review.</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>Reduces privilege exposure by avoiding routine use of full instance administrator accounts for Agent Hub management.</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>Agent Hub, Service account, Least privilege</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>generative_ai_acceleration</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="T11" s="3" t="inlineStr">
         <is>
           <t>Required permissions before deployment</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U11" s="3" t="n"/>
       <c r="V11" s="3" t="n"/>
       <c r="W11" s="3" t="n"/>
       <c r="X11" s="3" t="n"/>
       <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
+      <c r="AA11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4609,76 +4925,81 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
+          <t>Scope Agent Hub impersonation to specific groups; avoid wildcard outside sandbox testing.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
           <t>Administration &gt; Security &gt; Group &gt; Impersonation in WebApps &gt; Allowed groups</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>not_equals</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>Conceptual UI-based pointer; no literal diagnosis JSON field was given in the source for this setting.</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>Allowed groups field lists specific named groups relevant to Agent Hub users rather than a wildcard.</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>Allowed groups field is set to '.*' in what appears to be a production environment.</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>If group impersonation settings are not captured in the diagnosis, flag needs_manual_review and recommend checking Administration &gt; Security &gt; Group directly.</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>Using '.*' allows impersonation of all groups, an overly broad security exposure outside of sandbox/testing contexts.</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>Agent Hub, Impersonation, WebApps, Security groups</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>generative_ai_acceleration</t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="S12" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t>WebApp impersonation</t>
         </is>
       </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="n"/>
       <c r="W12" s="3" t="n"/>
       <c r="X12" s="3" t="n"/>
       <c r="Y12" s="3" t="n"/>
       <c r="Z12" s="3" t="n"/>
+      <c r="AA12" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4691,7 +5012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4700,26 +5021,27 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
     <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4755,100 +5077,105 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>statement_short</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>parameter_hint</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>operator</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>expected_value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>expected_condition_notes</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>supporting_evidence</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>contradicting_evidence</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>insufficient_evidence_handling</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rationale</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dataiku_concepts</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>source_document</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>source_page</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ambiguity_notes</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>validation_status</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>evidence_found</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>validated_by</t>
         </is>
@@ -4887,76 +5214,81 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>Replace the default H2 runtime database with external PostgreSQL for production readiness.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; internalDatabase.type</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Also verify maxPooledExternalConnections (general-settings.json) is at least 2x the postgresql.conf max_connections value (Cloud Stacks default max_connections=500), and that a backup process synced with DSS backups exists.</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>general-settings.json shows internalDatabase.type = PostgreSQL (external or DCS-managed); maxPooledExternalConnections &gt;= 2x postgres max_connections; documented backup process aligned with DSS backups.</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>internalDatabase field absent or shows internal H2 in use without an external Postgres configured; maxPooledExternalConnections too low relative to max_connections; no DB backup process.</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>If general-settings.json is unavailable or DB type cannot be determined, flag needs_manual_review and request the customer's postgresql.conf max_connections value and backup policy.</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>H2 does not scale well and complicates backup/resilience; PostgreSQL is required for production readiness.</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>runtime database, PostgreSQL, H2, backup</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>1, 2</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Postgres runtime database | MUST HAVE; Postgres runtime database | MUST HAVE</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
       <c r="W2" s="3" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
+      <c r="AA2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4991,80 +5323,85 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>Configure the metastore flavor (Hive, Glue, or internal) appropriate to the environment.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; metastoreCatalogsSettings.flavor</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>one_of</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Hive (Hadoop cluster) | Glue (AWS with proper integration) | DSS internal (otherwise)</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Correct value is context-dependent on infrastructure; also verify via Administration &gt; Settings &gt; Metastore catalogs UI.</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>flavor value matches environment type (Hive for Hadoop, Glue for properly-integrated AWS, else DSS internal); a test dataset sync confirms managed datasets sync to the metastore.</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>flavor mismatched with environment (e.g., Glue configured without proper AWS integration, or DSS internal used when Hive/Glue would be appropriate); sync test fails.</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>If environment type or metastoreCatalogsSettings is not present in the diagnosis, flag needs_manual_review and confirm with the customer during interview.</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Correct metastore selection ensures managed dataset metadata is properly synced and available for query engines.</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>metastore, Hive, Glue, managed datasets</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>2, 3</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Metastore is configured | NICE TO HAVE; Metastore is configured | NICE TO HAVE</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>Expected flavor value is not a fixed constant but depends on customer's infrastructure, so the check requires contextual knowledge of the environment.</t>
         </is>
       </c>
-      <c r="V3" s="3" t="n"/>
       <c r="W3" s="3" t="n"/>
       <c r="X3" s="3" t="n"/>
       <c r="Y3" s="3" t="n"/>
       <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -5099,76 +5436,81 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>Check whether Flow PDF/image export is configured and discuss enabling it if not.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; graphicsExportsEnabled</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Desired state is contextual on client needs; can also confirm via the Flow Actions &gt; Export to PDF/Image UI option.</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>graphicsExportsEnabled=true in general-settings.json, or the Export to PDF/Image option is visible in the Flow Actions menu.</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>graphicsExportsEnabled=false with no documented discussion or decision with the client about whether the feature is desired.</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>If the field is absent from the diagnosis, flag needs_manual_review and verify via the UI or ask the customer.</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Feature must be explicitly configured; disabling it may be acceptable if the client doesn't need it, hence nice to have.</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>graphics export, Flow</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>Graphics export configured | NICE TO HAVE</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5201,62 +5543,67 @@
           <t>An admin project should be set up to automatically clean up accumulated logs and idle Jupyter kernels on a schedule, per the Setup Maintenance Jobs wiki.</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Set up a scheduled admin project to clean up logs and idle Jupyter kernels.</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Presence of a dedicated admin/maintenance project with scenarios scheduled to clean logs and idle kernels; scenario run history shows regular execution.</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>No maintenance project exists, or disk usage/log data shows unbounded growth of logs or idle Jupyter kernels.</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis doesn't include a project list or scenario details, flag needs_manual_review and ask the customer to confirm existence of a scheduled cleanup project.</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Without cleanup, logs and idle kernels accumulate over time causing resource exhaustion.</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>admin project, garbage collection, scenarios, disk usage</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>3, 4</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Admin project - garbage collection | MUST HAVE; Admin project - garbage collection | MUST HAVE</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n"/>
       <c r="W5" s="3" t="n"/>
       <c r="X5" s="3" t="n"/>
       <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -5289,62 +5636,67 @@
           <t>Routine backups of DSS data must be configured for every DSS node to ensure data availability; for DCS installs, verify via Fleet Manager Instances &gt; Settings &gt; Snapshots, and for custom installs request backup policy details directly from the client.</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Configure routine backups of DSS data for every node to ensure data availability.</t>
+        </is>
+      </c>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>For DCS: Fleet Manager &gt; Instances &gt; Settings &gt; Snapshots shows a scheduled snapshot policy. For custom installs: a documented backup policy/cron job covering the DSS data directory is provided by the customer.</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>No snapshot schedule configured in Fleet Manager, or the customer has no documented backup process for a custom install.</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>If backup configuration isn't visible in the diagnosis (common for custom installs), flag needs_manual_review and request the client's backup policy documentation.</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>Backups ensure business continuity and data availability in case of failure.</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>backup, Fleet Manager, snapshots</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>4, 5</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>Environment Backup | MUST HAVE; Environment Backup | MUST HAVE</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U6" s="3" t="n"/>
       <c r="V6" s="3" t="n"/>
       <c r="W6" s="3" t="n"/>
       <c r="X6" s="3" t="n"/>
       <c r="Y6" s="3" t="n"/>
       <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -5377,62 +5729,67 @@
           <t>Verify that the Instance Sanity Check feature is used to detect instance configuration problems, accessible via Administration &gt; Maintenance &gt; Instance Sanity Check.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Use Instance Sanity Check periodically to detect instance configuration problems.</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Evidence that the customer has run the Instance Sanity Check periodically and addressed reported issues (e.g., DiagParser3 sanity check output showing no unresolved critical issues).</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>No record of Instance Sanity Check usage, or reported issues left unresolved for extended periods.</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis doesn't include sanity check results, flag needs_manual_review and check DiagParser3 or the Administration UI directly.</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Regular use helps proactively detect instance configuration issues before they cause problems.</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>Instance Sanity Check</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>5, 6</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>Usage of Instance Sanity Check | NICE TO HAVE; Usage of Instance Sanity Check | NICE TO HAVE</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n"/>
       <c r="W7" s="3" t="n"/>
       <c r="X7" s="3" t="n"/>
       <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="3" t="n"/>
+      <c r="AA7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -5465,62 +5822,67 @@
           <t>Review recent backend.log files (including rotated/zipped logs) for ERROR or FATAL level entries indicating systemic issues such as repeating stack traces, connection failures, or plugin crashes; investigate patterns that recur frequently even without explicit user complaints.</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Review backend.log for recurring ERROR/FATAL entries indicating systemic stability issues.</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>backend.log and rotated logs show few or no ERROR/FATAL entries, or only isolated non-recurring errors; AI Log Analysis in DiagParser3 shows no systemic issue flagged.</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Frequent recurring ERROR/FATAL entries (e.g., the same stack trace dozens of times per day), repeated connection failures, or plugin crashes.</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>If logs aren't included or available in the diagnosis bundle, flag needs_manual_review and request the backend.log files directly.</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>A high volume of repeated errors often points to a systemic issue that needs to be addressed before it impacts instance stability.</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>backend.log, AI Log Analysis, DiagParser3</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>6, 7</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>Backend.log Errors | MUST HAVE; Backend.log Errors | MUST HAVE</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U8" s="3" t="n"/>
       <c r="V8" s="3" t="n"/>
       <c r="W8" s="3" t="n"/>
       <c r="X8" s="3" t="n"/>
       <c r="Y8" s="3" t="n"/>
       <c r="Z8" s="3" t="n"/>
+      <c r="AA8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -5555,80 +5917,85 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
+          <t>Size backend.xmx per the memory heuristic, at least 3x the config folder size.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
           <t>install.ini &gt; backend.xmx</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>greater_than_or_equal</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>per Cloud Stacks heuristic tier (4g/8g/16g based on system RAM) and &gt;=3x config folder size</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>Also verify jek.xmx/fek.xmx are not oversized, and that xmx avoids the 32GB&lt;=xmx&lt;48GB dead zone (jump to 48GB instead) due to Java Ordinary Object Pointer behavior.</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>install.ini backend.xmx matches or exceeds the recommended tier for system memory, is &gt;=3x config folder size, and avoids the 32-48GB dead zone; no OutOfMemoryError entries in backend.log.</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>backend.xmx set below the recommended heuristic, falls in the 32GB-48GB dead zone, or backend.log shows recurring 'OutOfMemoryError: Java heap space' / 'OutOfMemoryError: GC Overhead limit exceeded' entries.</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>If install.ini or system memory info is not present in the diagnosis, flag needs_manual_review and request system specs and install.ini contents.</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>Insufficient or misconfigured heap sizing leads to OutOfMemory errors and instability; oversizing into the 32-48GB range paradoxically reduces available memory due to JVM pointer compression behavior.</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>backend.xmx, jek.xmx, fek.xmx, JVM memory, OutOfMemoryError</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R9" s="3" t="inlineStr">
+      <c r="S9" s="3" t="inlineStr">
         <is>
           <t>7, 8</t>
         </is>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="T9" s="3" t="inlineStr">
         <is>
           <t>Backend Xmx | MUST HAVE; Backend Xmx | MUST HAVE</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n"/>
       <c r="W9" s="3" t="n"/>
       <c r="X9" s="3" t="n"/>
       <c r="Y9" s="3" t="n"/>
       <c r="Z9" s="3" t="n"/>
+      <c r="AA9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -5663,76 +6030,81 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>Size Max Jobs and Max Activities via the memory framework; never set Max Jobs to zero.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; maxRunningJobs</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>not_equals</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>Also verify general-settings.json &gt; maxRunningActivities falls within 30-50, and maxRunningActivitiesPerJob is at the default of 5 unless justified. Front-end equivalent: Administration &gt; Settings &gt; Resources control &gt; Concurrent Activities.</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>maxRunningJobs set to a positive nonzero value derived from the 5-step memory sizing framework; maxRunningActivities within 30-50; maxRunningActivitiesPerJob at 5 (or a justified alternative).</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>maxRunningJobs is 0 or blank (critical stability risk); maxRunningActivities is outside 30-50 without justification; sizing doesn't account for available host memory, risking OOM.</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>If these general-settings.json values are missing from the diagnosis, flag needs_manual_review and check the Administration &gt; Settings &gt; Resources control UI directly.</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>Improperly sized flow limits risk instance-wide Out-Of-Memory crashes; Max Jobs=0 disables protection entirely.</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>Flow limits, Max Jobs, Max Activities, CGroups, JEK, memory sizing</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t>8, 9, 10, 11</t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>Flow parallelism | MUST HAVE; Flow parallelism | MUST HAVE; Flow parallelism | MUST HAVE; Flow parallelism | MUST HAVE</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U10" s="3" t="n"/>
       <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="n"/>
       <c r="X10" s="3" t="n"/>
       <c r="Y10" s="3" t="n"/>
       <c r="Z10" s="3" t="n"/>
+      <c r="AA10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5767,80 +6139,85 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
+          <t>Leave default connection and engine preferences blank unless a specific use case justifies them.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; defaultDatasetCreationSettings / recipeEnginesPreferences (preferedConnection, forcedPreferedConnection, preferedUploadConnection, preferedStorageFormats)</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>unset/blank unless justified specific use case</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>These keys may be entirely absent from general-settings.json if left blank, which is the expected default state.</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>Keys absent or blank in general-settings.json, or if set, a documented specific use case justifies the value (e.g., not forcing storage to a local server).</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>preferedConnection/forcedPreferedConnection set to force local server storage, or preferred engine changed without clear justification, especially on v12+ instances.</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>If this section of general-settings.json is missing from the diagnosis, flag needs_manual_review and check the Administration &gt; Settings &gt; Engines &amp; connections UI.</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>These settings default to blank for good reason; forcing values can cause breaking changes or performance issues (e.g., forcing local storage).</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>default dataset creation, recipe engine preferences, connections</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t>12, 13, 14</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="T11" s="3" t="inlineStr">
         <is>
           <t>Preferreds and Defaults | NICE TO HAVE; Preferreds and Defaults | NICE TO HAVE; Preferreds and Defaults | NICE TO HAVE</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="V11" s="3" t="inlineStr">
         <is>
           <t>Expected value is contextual ('reasonable values' if set), not a fixed constant, so the check requires judgment.</t>
         </is>
       </c>
-      <c r="V11" s="3" t="n"/>
       <c r="W11" s="3" t="n"/>
       <c r="X11" s="3" t="n"/>
       <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
+      <c r="AA11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -5875,76 +6252,81 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
+          <t>Remove the filesystem_root connection unless actively used, replacing it with a scoped connection.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
           <t>connections.json &gt; filesystem_root</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>not_exists</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>removed (unless replaced by a scoped connection after confirming no active project usage)</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>Check usage via Administration -&gt; Monitoring before deletion.</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>filesystem_root connection absent from the connections list, or confirmed unused and removed; if it was in use, a dedicated scoped connection was created to replace it.</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>filesystem_root connection still present and either unused (should have been deleted) or in use without a safer scoped replacement.</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>If the connections list isn't in the diagnosis, flag needs_manual_review and check the Administration &gt; Connections UI directly.</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>The filesystem_root connection exposes the entire server filesystem, posing a security and stability risk.</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>connections, filesystem_root, security</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="S12" s="3" t="inlineStr">
         <is>
           <t>14, 15</t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t>Remove filesystem_root connection | MUST HAVE; Remove filesystem_root connection | MUST HAVE</t>
         </is>
       </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="n"/>
       <c r="W12" s="3" t="n"/>
       <c r="X12" s="3" t="n"/>
       <c r="Y12" s="3" t="n"/>
       <c r="Z12" s="3" t="n"/>
+      <c r="AA12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -5979,76 +6361,81 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
+          <t>Enable Details readable by and set the correct HDFS interface for cloud storage connections.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
           <t>cloud storage connection settings &gt; detailsReadableBy</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Also verify HDFS interface setting matches the cloud storage type mapping (S3A/EMRFS for S3, ABFS/WASB for Azure Blob, GS for GCS).</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>Cloud storage connections show 'Details readable by' enabled and the correct HDFS interface configured per the platform/type mapping.</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>'Details readable by' disabled, forcing all traffic through the DSS node (performance bottleneck), or a mismatched/incorrect HDFS interface for the cloud storage type.</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>If connection details aren't in the diagnosis, flag needs_manual_review and check Administration &gt; Connections for each cloud storage connection.</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>Without 'Details readable by', all data traffic funnels through the single DSS node creating a performance bottleneck; correct HDFS interface ensures compatibility with distributed compute engines.</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>cloud storage connections, details readable by, HDFS interface, S3, Azure Blob, GCS</t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="S13" s="3" t="inlineStr">
         <is>
           <t>15, 16</t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="T13" s="3" t="inlineStr">
         <is>
           <t>Cloud Object Storage | MUST HAVE; Cloud Object Storage | MUST HAVE</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U13" s="3" t="n"/>
       <c r="V13" s="3" t="n"/>
       <c r="W13" s="3" t="n"/>
       <c r="X13" s="3" t="n"/>
       <c r="Y13" s="3" t="n"/>
       <c r="Z13" s="3" t="n"/>
+      <c r="AA13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -6083,76 +6470,81 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
+          <t>Enable Automatic fast-write, Spark native integration, and UDF support for Snowflake connections.</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
           <t>Snowflake connection settings &gt; enableAutomaticFastWrite / enableSparkNativeIntegration / enableUDF, and cloud storage connection &gt; detailsReadableBy</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>Cloud storage connection authentication must also meet the Automatic fast-write requirements per Dataiku documentation.</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>Snowflake connection shows Automatic fast-write, Spark native integration, and UDF enabled where applicable, and the cloud storage connection has 'Details readable by' enabled with compatible auth.</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>These settings disabled without justification, or cloud storage auth incompatible with fast-write requirements, limiting functionality (e.g., no Snowpark/Spark native access).</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>If Snowflake connection settings aren't present in the diagnosis, flag needs_manual_review and check Administration &gt; Connections for the Snowflake connection.</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>These settings enable performant, parallel data movement and advanced compute integration (Snowpark, Spark) rather than slow single-threaded funneling.</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>Snowflake, Automatic fast-write, Spark native integration, details readable by</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
+      <c r="R14" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R14" s="3" t="inlineStr">
+      <c r="S14" s="3" t="inlineStr">
         <is>
           <t>16, 17</t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="T14" s="3" t="inlineStr">
         <is>
           <t>Snowflake | MUST HAVE; Snowflake | MUST HAVE</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="n"/>
       <c r="W14" s="3" t="n"/>
       <c r="X14" s="3" t="n"/>
       <c r="Y14" s="3" t="n"/>
       <c r="Z14" s="3" t="n"/>
+      <c r="AA14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -6187,76 +6579,81 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
+          <t>Enable Automatic fast-write and Details readable by for Databricks connections.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
           <t>Databricks connection settings &gt; enableAutomaticFastWrite, and cloud storage connection &gt; detailsReadableBy</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Cloud storage connection authentication must also meet the Automatic fast-write requirements per Dataiku documentation.</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>Databricks connection shows Automatic fast-write enabled, and the cloud storage connection has 'Details readable by' enabled with compatible auth.</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>Automatic fast-write or 'Details readable by' disabled, or cloud storage auth incompatible with fast-write requirements.</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>If Databricks connection settings aren't present in the diagnosis, flag needs_manual_review and check Administration &gt; Connections for the Databricks connection.</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>These settings enable performant, parallel data movement between DSS and Databricks rather than slow single-threaded funneling.</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>Databricks, Automatic fast-write, details readable by</t>
         </is>
       </c>
-      <c r="Q15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr">
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t>17, 18</t>
         </is>
       </c>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="T15" s="3" t="inlineStr">
         <is>
           <t>Databricks | MUST HAVE; Databricks | MUST HAVE</t>
         </is>
       </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U15" s="3" t="n"/>
       <c r="V15" s="3" t="n"/>
       <c r="W15" s="3" t="n"/>
       <c r="X15" s="3" t="n"/>
       <c r="Y15" s="3" t="n"/>
       <c r="Z15" s="3" t="n"/>
+      <c r="AA15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -6291,76 +6688,81 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>Enable Automatic fast-write for Redshift, BigQuery, and Synapse connections.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
           <t>Redshift/BigQuery/Synapse connection settings &gt; enableAutomaticFastWrite</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>Cloud storage connection authentication must also meet the Automatic fast-write requirements per Dataiku documentation; Redshift Fast Path is write-only and does not apply to unload.</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>Redshift/BigQuery/Synapse connection shows Automatic fast-write enabled and compatible cloud storage authentication.</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>Automatic fast-write disabled, or cloud storage auth incompatible with fast-write requirements.</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>If these connection settings aren't present in the diagnosis, flag needs_manual_review and check Administration &gt; Connections for the relevant connection.</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>Automatic fast-write enables performant, parallel data movement rather than slow single-threaded funneling.</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>Redshift, BigQuery, Synapse, Automatic fast-write</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R16" s="3" t="inlineStr">
+      <c r="S16" s="3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S16" s="3" t="inlineStr">
+      <c r="T16" s="3" t="inlineStr">
         <is>
           <t>Amazon Redshift, Google BigQuery, Azure Synapse | MUST HAVE</t>
         </is>
       </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="U16" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U16" s="3" t="n"/>
       <c r="V16" s="3" t="n"/>
       <c r="W16" s="3" t="n"/>
       <c r="X16" s="3" t="n"/>
       <c r="Y16" s="3" t="n"/>
       <c r="Z16" s="3" t="n"/>
+      <c r="AA16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -6393,66 +6795,71 @@
           <t>Discuss disaster recovery (DR) and high-availability (HA) considerations with the client based on the criticality of workloads: verify backup/snapshot scheduling against a defined RPO, existence of tested and possibly automated recovery procedures meeting RTO, and for active/passive HA setups, validate redundant identical servers without a common SPOF, shared/replicated storage, cluster/network failover management with fencing and a vanity/floating IP, and active monitoring/alerting (noting Dataiku does not provide monitoring). Do not commit to implementing a DR solution during the review sessions themselves.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Discuss backup, recovery, and high-availability requirements with the client based on workload criticality.</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>Documented backup/snapshot schedule meeting RPO, tested recovery/failover procedures meeting RTO, and for HA setups: redundant identical servers without shared SPOF, properly configured shared/replicated storage, cluster management with fencing, a vanity URL/floating IP, and active monitoring.</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>No RPO/RTO defined, infrequent or untested backups, no documented recovery procedure, or HA setup missing key components (shared SPOF present, no fencing mechanism, no monitoring).</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>If DR/HA plans are not discussed or documented in available materials, flag needs_manual_review and schedule a dedicated discussion with the client; do not commit to building a DR solution as part of the review itself.</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>HA/DR planning ensures business continuity; horizontal HA is not natively possible for stateful DSS instances, making backup/recovery discipline critical.</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>disaster recovery, high availability, RPO, RTO, failover</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>scalable_performance_ops</t>
         </is>
       </c>
-      <c r="R17" s="3" t="inlineStr">
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t>18, 19, 20</t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="T17" s="3" t="inlineStr">
         <is>
           <t>Disaster Recovery Strategy (Placeholder) | NICE TO HAVE; Disaster Recovery Strategy (Placeholder) | NICE TO HAVE; Disaster Recovery Strategy (Placeholder) | NICE TO HAVE</t>
         </is>
       </c>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
+      <c r="V17" s="3" t="inlineStr">
         <is>
           <t>Section heading is marked '(Placeholder)', suggesting the content may be incomplete or subject to revision in the source document.</t>
         </is>
       </c>
-      <c r="V17" s="3" t="n"/>
       <c r="W17" s="3" t="n"/>
       <c r="X17" s="3" t="n"/>
       <c r="Y17" s="3" t="n"/>
       <c r="Z17" s="3" t="n"/>
+      <c r="AA17" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6465,7 +6872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6474,26 +6881,27 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
     <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6529,100 +6937,105 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>statement_short</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>parameter_hint</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>operator</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>expected_value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>expected_condition_notes</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>supporting_evidence</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>contradicting_evidence</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>insufficient_evidence_handling</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rationale</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dataiku_concepts</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>source_document</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>source_page</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ambiguity_notes</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>validation_status</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>evidence_found</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>validated_by</t>
         </is>
@@ -6661,72 +7074,77 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>Set security.hideErrorStacks to true to stop exposing internal error details to users.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; security.hideErrorStacks</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>general-settings.json contains a "security" object with "hideErrorStacks": true.</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>The "security" key is absent, or present without "hideErrorStacks", or it is explicitly set to false, meaning stack traces are still shown to logged-in users.</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>If the diagnosis does not include the contents of general-settings.json, flag as needs_manual_review, since absence of the key means the DSS-shipped default (stack traces shown) applies.</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>By default DSS sends backend error stacks to logged-in users to make debugging and understanding easier; this can be turned off to prevent internal implementation details from leaking to users.</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>general-settings.json, security settings, error handling</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>advanced_security_options</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>1, 2</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Hiding error stacks; Hiding error stacks</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
       <c r="W2" s="3" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
+      <c r="AA2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -6761,72 +7179,77 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>Set security.hideVersionStringsWhenNotLogged to true to hide the DSS version from anonymous users.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>general-settings.json &gt; security.hideVersionStringsWhenNotLogged</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>general-settings.json "security" object contains "hideVersionStringsWhenNotLogged": true.</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>The key is absent or set to false, meaning version info is still sent to non-logged-in users.</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>If general-settings.json content is not present in the diagnosis, flag as needs_manual_review; the default (version info exposed) applies absent this key.</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>By default DSS sends version information even to non-logged in users; this can be disabled to reduce fingerprinting of the DSS instance.</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>general-settings.json, security settings, version disclosure</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>advanced_security_options</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Hiding version info</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
       <c r="W3" s="3" t="n"/>
       <c r="X3" s="3" t="n"/>
       <c r="Y3" s="3" t="n"/>
       <c r="Z3" s="3" t="n"/>
+      <c r="AA3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -6836,7 +7259,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>nice_to_have</t>
+          <t>must_have</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -6846,95 +7269,100 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Cookie &amp; Transport Security</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Using secure cookies</t>
+          <t>Expiring sessions</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>By default, DSS login cookies do not carry the Secure flag, meaning they could be sent over unencrypted HTTP. Where HTTPS is used for all users (natively or via reverse proxy), administrators should set security.secureCookies to true in general-settings.json so that session cookies are only ever transmitted over secure connections, enhancing session security.</t>
+          <t>DSS can be configured to expire user sessions after a maximum duration since login and/or after a period of inactivity, via Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management ('Maximum session duration' and 'Idle timeout'), noting this can cause lost work if a session expires mid-edit.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>general-settings.json &gt; security.secureCookies</t>
+          <t>Configure maximum session duration and idle timeout to automatically expire user sessions.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>equals</t>
+          <t>Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management &gt; Maximum session duration / Idle timeout</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Should only be enabled once DSS is served exclusively over HTTPS everywhere (natively or via reverse proxy); enabling without full HTTPS coverage would break login for HTTP-only clients.</t>
-        </is>
-      </c>
+          <t>exists</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>configured to a finite, non-default timeout value</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>general-settings.json shows secureCookies: true under the security top-level section, ideally alongside evidence that DSS/its reverse proxy enforces HTTPS for all users.</t>
+          <t>The source does not mandate a specific numeric threshold, only that admins may configure these fields; treat as satisfied if either or both values are set to a finite duration rather than left unlimited/unset.</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>secureCookies is false or absent while HTTPS is confirmed used for all users, or secureCookies is true without any HTTPS confirmation.</t>
+          <t>Diagnosis or exported settings show a configured, finite 'Maximum session duration' and/or 'Idle timeout' value in session management settings.</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>If HTTPS usage status or the general-settings.json security section is not visible in the diagnosis file, flag as needs_manual_review.</t>
+          <t>Session management settings show these fields unset or set to unlimited/no-expiration.</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Secure cookies prevent cookies from being transmitted over unencrypted connections, reducing session hijacking risk when HTTPS is in use; they ensure the browser never sends the session cookie over unsecured connections, further securing user sessions.</t>
+          <t>Session management configuration is often not captured in standard diagnostic exports (it's a UI/DB-stored setting, not a config file key); flag as needs_manual_review, noting the source's own caveat about potential lost work from expiring sessions.</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>secure cookies, general-settings.json, security settings, cookies, HTTPS</t>
+          <t>Session expiration limits how long a stolen or abandoned session remains valid, though the source warns it can cause lost in-progress work (including complications with open Jupyter notebooks).</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>advanced_security_options, security_permissions_compliance</t>
+          <t>session management, user login &amp; provisioning</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>6, 7, 2, 3</t>
+          <t>advanced_security_options</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>Secure Cookies | NICE TO HAVE; Secure Cookies | NICE TO HAVE (Review steps); Using secure cookies; Using secure cookies</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>Expiring sessions</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Source documents disagree on priority: the security_permissions_compliance document explicitly tags this NICE TO HAVE, while the advanced_security_options document treats it as must_have via inferred reasoning about session-security hardening. Per merge policy, the explicit_in_source classification (nice_to_have) was retained; downstream reviewers should be aware of this discrepancy when weighing severity.</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>No literal config-file key is given for this UI-only setting, and no specific recommended numeric threshold is provided, so the expected_condition is a best-effort conceptual pointer to the UI path rather than a literal field.</t>
+        </is>
+      </c>
       <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -6959,90 +7387,95 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Expiring sessions</t>
+          <t>Forcing a single session per user</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>DSS can be configured to expire user sessions after a maximum duration since login and/or after a period of inactivity, via Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management ('Maximum session duration' and 'Idle timeout'), noting this can cause lost work if a session expires mid-edit.</t>
+          <t>By default DSS allows a user to be logged in from multiple sessions simultaneously; administrators can enable 'Force single session per user' (Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management) so that a new login terminates all of that user's other active sessions.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management &gt; Maximum session duration / Idle timeout</t>
+          <t>Enable Force single session per user so new logins terminate other active sessions.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>exists</t>
+          <t>Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management &gt; Force single session per user</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>configured to a finite, non-default timeout value</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>The source does not mandate a specific numeric threshold, only that admins may configure these fields; treat as satisfied if either or both values are set to a finite duration rather than left unlimited/unset.</t>
-        </is>
-      </c>
+          <t>equals</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Diagnosis or exported settings show a configured, finite 'Maximum session duration' and/or 'Idle timeout' value in session management settings.</t>
+          <t>This is a UI toggle, not a documented general-settings.json/dip.properties key in the source text.</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Session management settings show these fields unset or set to unlimited/no-expiration.</t>
+          <t>Session management settings show 'Force single session per user' enabled.</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Session management configuration is often not captured in standard diagnostic exports (it's a UI/DB-stored setting, not a config file key); flag as needs_manual_review, noting the source's own caveat about potential lost work from expiring sessions.</t>
+          <t>The setting is shown as disabled (default), allowing multiple concurrent sessions per user.</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>Session expiration limits how long a stolen or abandoned session remains valid, though the source warns it can cause lost in-progress work (including complications with open Jupyter notebooks).</t>
+          <t>This UI-only toggle is often not captured in diagnostic exports; flag as needs_manual_review, noting the default is disabled (multiple sessions allowed).</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
+          <t>By default users can have multiple simultaneous sessions; forcing a single session per user terminates other sessions on new login, reducing exposure from stale or hijacked sessions.</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
           <t>session management, user login &amp; provisioning</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>advanced_security_options</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>Expiring sessions</t>
-        </is>
-      </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
+          <t>Forcing a single session per user</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>No literal config-file key is given for this UI-only setting, and no specific recommended numeric threshold is provided, so the expected_condition is a best-effort conceptual pointer to the UI path rather than a literal field.</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="n"/>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>No literal config-file key is given for this UI-only setting.</t>
+        </is>
+      </c>
       <c r="W5" s="3" t="n"/>
       <c r="X5" s="3" t="n"/>
       <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -7052,7 +7485,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>must_have</t>
+          <t>nice_to_have</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -7062,88 +7495,88 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Session Management</t>
+          <t>User Isolation Framework</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Forcing a single session per user</t>
+          <t>Restricting visibility of groups and users</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>By default DSS allows a user to be logged in from multiple sessions simultaneously; administrators can enable 'Force single session per user' (Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management) so that a new login terminates all of that user's other active sessions.</t>
+          <t>By default, all logged-in DSS users can view the full list of groups and users (useful for adding groups to projects and mentioning users); administrators can set security.restrictUsersAndGroupsVisibility to true in general-settings.json to limit visibility to admins, one's own groups/their members, and users who share a project, though this is explicitly a best-effort feature without a guarantee of perfect isolation.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management &gt; Force single session per user</t>
+          <t>Set restrictUsersAndGroupsVisibility to true to limit visibility of the full user/group list.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
+          <t>general-settings.json &gt; security.restrictUsersAndGroupsVisibility</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>This is a UI toggle, not a documented general-settings.json/dip.properties key in the source text.</t>
-        </is>
-      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Session management settings show 'Force single session per user' enabled.</t>
+          <t>Best-effort feature; does not guarantee full isolation and reduces convenience features like universal user mentions and easy group-adding for project owners, so instances may deliberately leave it disabled.</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>The setting is shown as disabled (default), allowing multiple concurrent sessions per user.</t>
+          <t>general-settings.json "security" object contains "restrictUsersAndGroupsVisibility": true.</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>This UI-only toggle is often not captured in diagnostic exports; flag as needs_manual_review, noting the default is disabled (multiple sessions allowed).</t>
+          <t>The key is absent or false, meaning all logged-in users can see the full list of groups and users.</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>By default users can have multiple simultaneous sessions; forcing a single session per user terminates other sessions on new login, reducing exposure from stale or hijacked sessions.</t>
+          <t>If general-settings.json content is not present in the diagnosis, flag as needs_manual_review; the default (unrestricted visibility) applies absent this key.</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>session management, user login &amp; provisioning</t>
+          <t>Restricting visibility of the global user/group list can reduce information available for social-engineering/enumeration, though the source notes it is best-effort and does not guarantee full isolation.</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
+          <t>general-settings.json, security settings, user/group visibility</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
           <t>advanced_security_options</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>Forcing a single session per user</t>
+          <t>3, 4</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>Restricting visibility of groups and users; Restricting visibility of groups and users</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>No literal config-file key is given for this UI-only setting.</t>
+          <t>high</t>
         </is>
       </c>
       <c r="V6" s="3" t="n"/>
@@ -7151,6 +7584,7 @@
       <c r="X6" s="3" t="n"/>
       <c r="Y6" s="3" t="n"/>
       <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -7170,88 +7604,88 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>User Isolation Framework</t>
+          <t>Session &amp; Logout UX</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Restricting visibility of groups and users</t>
+          <t>Redirecting to a custom URL after logout</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>By default, all logged-in DSS users can view the full list of groups and users (useful for adding groups to projects and mentioning users); administrators can set security.restrictUsersAndGroupsVisibility to true in general-settings.json to limit visibility to admins, one's own groups/their members, and users who share a project, though this is explicitly a best-effort feature without a guarantee of perfect isolation.</t>
+          <t>By default, users are redirected to a standard DSS-hosted page after logout; administrators can configure security.postLogoutBehavior (CUSTOM_URL for a GET redirect or CUSTOM_URL_POST for a POST request aligned with OpenID Connect RP-Initiated Logout) together with security.postLogoutCustomURL (must be an http/https URL) in general-settings.json to redirect users elsewhere, with DSS validating these settings on save/load and falling back to the default page on invalid values.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>general-settings.json &gt; security.restrictUsersAndGroupsVisibility</t>
+          <t>Configure postLogoutBehavior and postLogoutCustomURL to redirect users after logout.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>equals</t>
+          <t>general-settings.json &gt; security.postLogoutBehavior / security.postLogoutCustomURL</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Best-effort feature; does not guarantee full isolation and reduces convenience features like universal user mentions and easy group-adding for project owners, so instances may deliberately leave it disabled.</t>
-        </is>
-      </c>
+          <t>one_of</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM_URL, CUSTOM_URL_POST</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>general-settings.json "security" object contains "restrictUsersAndGroupsVisibility": true.</t>
+          <t>postLogoutCustomURL is required and must be an http/https URL when postLogoutBehavior is CUSTOM_URL or CUSTOM_URL_POST; DSS validates these settings on save and on load, falling back to the default DSS logged-out page if invalid.</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>The key is absent or false, meaning all logged-in users can see the full list of groups and users.</t>
+          <t>general-settings.json "security" object contains postLogoutBehavior set to CUSTOM_URL or CUSTOM_URL_POST along with a valid http/https postLogoutCustomURL.</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>If general-settings.json content is not present in the diagnosis, flag as needs_manual_review; the default (unrestricted visibility) applies absent this key.</t>
+          <t>The keys are absent (default DSS logged-out page used) or postLogoutCustomURL is invalid, in which case DSS falls back to default behavior anyway.</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Restricting visibility of the global user/group list can reduce information available for social-engineering/enumeration, though the source notes it is best-effort and does not guarantee full isolation.</t>
+          <t>If general-settings.json content is not present in the diagnosis, flag as needs_manual_review; absence means the default logout page is used, which is not a security concern.</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>general-settings.json, security settings, user/group visibility</t>
+          <t>Allows organizations to redirect users to a branded or external page after logout instead of the DSS default logged-out page.</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
+          <t>general-settings.json, security settings, logout, OpenID Connect</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
           <t>advanced_security_options</t>
         </is>
       </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>3, 4</t>
-        </is>
-      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>Restricting visibility of groups and users; Restricting visibility of groups and users</t>
+          <t>4, 5</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
+          <t>Redirecting to a custom URL after logout; Redirecting to a custom URL after logout</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
           <t>high</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>Note: despite the subtopic label 'User Isolation Framework' shared with SEC-002, this setting concerns UI-level visibility of the group/user directory and is a distinct checkable practice from the OS-level impersonation-based User Isolation Framework covered in SEC-002.</t>
         </is>
       </c>
       <c r="V7" s="3" t="n"/>
@@ -7259,6 +7693,7 @@
       <c r="X7" s="3" t="n"/>
       <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="3" t="n"/>
+      <c r="AA7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -7268,7 +7703,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>nice_to_have</t>
+          <t>must_have</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -7278,91 +7713,96 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Session &amp; Logout UX</t>
+          <t>Content Upload Restrictions</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Redirecting to a custom URL after logout</t>
+          <t>Restricting types of files that can be uploaded in wikis</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>By default, users are redirected to a standard DSS-hosted page after logout; administrators can configure security.postLogoutBehavior (CUSTOM_URL for a GET redirect or CUSTOM_URL_POST for a POST request aligned with OpenID Connect RP-Initiated Logout) together with security.postLogoutCustomURL (must be an http/https URL) in general-settings.json to redirect users elsewhere, with DSS validating these settings on save/load and falling back to the default page on invalid values.</t>
+          <t>By default, all logged-in DSS users can upload any type of file to wiki articles; administrators can restrict this by setting dku.wikis.authorizedUploadExtensions in dip.properties to a comma-separated allow-list of file extensions (e.g., png,jpg,jpeg,gif,txt,csv).</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>general-settings.json &gt; security.postLogoutBehavior / security.postLogoutCustomURL</t>
+          <t>Restrict wiki file uploads to an approved extension list via dip.properties.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>one_of</t>
+          <t>dip.properties &gt; dku.wikis.authorizedUploadExtensions</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>CUSTOM_URL, CUSTOM_URL_POST</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>postLogoutCustomURL is required and must be an http/https URL when postLogoutBehavior is CUSTOM_URL or CUSTOM_URL_POST; DSS validates these settings on save and on load, falling back to the default DSS logged-out page if invalid.</t>
-        </is>
-      </c>
+          <t>exists</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>restricted list of extensions (e.g., png,jpg,jpeg,gif,txt,csv)</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>general-settings.json "security" object contains postLogoutBehavior set to CUSTOM_URL or CUSTOM_URL_POST along with a valid http/https postLogoutCustomURL.</t>
+          <t>Default (unset) allows uploads of any file type; presence of this key with a restrictive list indicates the practice is followed.</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>The keys are absent (default DSS logged-out page used) or postLogoutCustomURL is invalid, in which case DSS falls back to default behavior anyway.</t>
+          <t>dip.properties contains dku.wikis.authorizedUploadExtensions set to a specific, restrictive comma-separated list of extensions.</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>If general-settings.json content is not present in the diagnosis, flag as needs_manual_review; absence means the default logout page is used, which is not a security concern.</t>
+          <t>The key is absent from dip.properties, meaning any file type can be uploaded to wiki articles.</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>Allows organizations to redirect users to a branded or external page after logout instead of the DSS default logged-out page.</t>
+          <t>If dip.properties content is not present in the diagnosis, flag as needs_manual_review; the default (unrestricted upload types) applies absent this key.</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>general-settings.json, security settings, logout, OpenID Connect</t>
+          <t>Restricting file types uploaded to wikis reduces the risk of malicious or unwanted file types being hosted and shared via the DSS wiki feature.</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
+          <t>dip.properties, wikis, file upload restrictions</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
           <t>advanced_security_options</t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>4, 5</t>
-        </is>
-      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>Redirecting to a custom URL after logout; Redirecting to a custom URL after logout</t>
+          <t>6</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
+          <t>Restricting types of files that can be uploaded in wikis</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U8" s="3" t="n"/>
       <c r="V8" s="3" t="n"/>
       <c r="W8" s="3" t="n"/>
       <c r="X8" s="3" t="n"/>
       <c r="Y8" s="3" t="n"/>
       <c r="Z8" s="3" t="n"/>
+      <c r="AA8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -7382,91 +7822,96 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Content Upload Restrictions</t>
+          <t>Data Exfiltration Controls</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Restricting types of files that can be uploaded in wikis</t>
+          <t>Restricting exports</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>By default, all logged-in DSS users can upload any type of file to wiki articles; administrators can restrict this by setting dku.wikis.authorizedUploadExtensions in dip.properties to a comma-separated allow-list of file extensions (e.g., png,jpg,jpeg,gif,txt,csv).</t>
+          <t>DSS can globally restrict export/copy features (regardless of project-level permissions) via a set of escalating dip.properties keys: disableAllDatasetExports, disableAllDataExports (implies the former), disableAllExports (implies both former), plus the independent disableCopySampleToClipboard and disableSQLNotebookCopyResultToClipboard keys for clipboard copying; the source explicitly warns this is only a 'best-effort' restriction since any user who can see data can still exfiltrate it, e.g. via copy/paste.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>dip.properties &gt; dku.wikis.authorizedUploadExtensions</t>
+          <t>Disable export and clipboard-copy keys in dip.properties to limit data exfiltration risk.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>exists</t>
+          <t>dip.properties &gt; dku.exports.disable*</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>restricted list of extensions (e.g., png,jpg,jpeg,gif,txt,csv)</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Default (unset) allows uploads of any file type; presence of this key with a restrictive list indicates the practice is followed.</t>
-        </is>
-      </c>
+          <t>one_of</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>dku.exports.disableAllDatasetExports=true; dku.exports.disableAllDataExports=true; dku.exports.disableAllExports=true; dku.exports.disableCopySampleToClipboard=true; dku.exports.disableSQLNotebookCopyResultToClipboard=true</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>dip.properties contains dku.wikis.authorizedUploadExtensions set to a specific, restrictive comma-separated list of extensions.</t>
+          <t>dku.exports.disableAllDatasetExports=true disables 'Download' export of datasets to files (CSV, Excel, Tableau Hyper, etc.), plus including datasets in project exports/bundle downloads and attaching datasets to emails in scenarios; other exports (ML data, schema, SQL queries, prepared data) remain possible. dku.exports.disableAllDataExports=true implies the previous key and additionally disables exports of prepared data or SQL query results, downloading files/zips from managed folders, and including datasets or managed folders in project exports/bundle downloads or scenario email attachments; ML data and schema exports remain possible. dku.exports.disableAllExports=true implies both previous keys and additionally disables exports of ML data and schemas, so essentially all dataset, prepared-data, SQL-query, ML data/schema, and managed-folder exports, downloads, bundle inclusions, and email attachments are disabled. dku.exports.disableCopySampleToClipboard=true disables copying data samples to the clipboard everywhere except SQL notebooks (default false, i.e. enabled). dku.exports.disableSQLNotebookCopyResultToClipboard=true disables copying results to the clipboard specifically in SQL notebooks (default false, i.e. enabled).</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>The key is absent from dip.properties, meaning any file type can be uploaded to wiki articles.</t>
+          <t>dip.properties contains one or more of the five dku.exports.disable* keys set to true, at a scope level (dataset/data/all) matching the organization's data-exfiltration risk tolerance.</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>If dip.properties content is not present in the diagnosis, flag as needs_manual_review; the default (unrestricted upload types) applies absent this key.</t>
+          <t>None of the dku.exports.disable* keys are present or set to true, meaning full export and clipboard-copy capabilities remain available to any user with data-view permission.</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Restricting file types uploaded to wikis reduces the risk of malicious or unwanted file types being hosted and shared via the DSS wiki feature.</t>
+          <t>dip.properties content is often not fully captured in diagnostics; if absent, flag as needs_manual_review. Importantly, even when these settings are enabled, treat this only as a risk-reduction control, not a guarantee: the source explicitly states export restriction is inherently 'best-effort' since a user who can view data can still exfiltrate it by other means (e.g., copy/paste).</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>dip.properties, wikis, file upload restrictions</t>
+          <t>Restricting export and clipboard-copy features reduces (but per the source's own warning, does not eliminate) the ability of authorized viewers to exfiltrate data out of DSS.</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
+          <t>dip.properties, exports, data exfiltration</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
           <t>advanced_security_options</t>
         </is>
       </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>Restricting types of files that can be uploaded in wikis</t>
+          <t>6, 7, 8</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
+          <t>Restricting exports; Restricting exports; Restricting exports</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n"/>
       <c r="W9" s="3" t="n"/>
       <c r="X9" s="3" t="n"/>
       <c r="Y9" s="3" t="n"/>
       <c r="Z9" s="3" t="n"/>
+      <c r="AA9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -7486,91 +7931,96 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Data Exfiltration Controls</t>
+          <t>Transport &amp; Browser Hardening</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Restricting exports</t>
+          <t>Setting security-related HTTP headers</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>DSS can globally restrict export/copy features (regardless of project-level permissions) via a set of escalating dip.properties keys: disableAllDatasetExports, disableAllDataExports (implies the former), disableAllExports (implies both former), plus the independent disableCopySampleToClipboard and disableSQLNotebookCopyResultToClipboard keys for clipboard copying; the source explicitly warns this is only a 'best-effort' restriction since any user who can see data can still exfiltrate it, e.g. via copy/paste.</t>
+          <t>DSS supports configuring standard security-related HTTP response headers (X-Frame-Options, Content-Security-Policy, X-XSS-Protection, X-Content-Type-Options, Strict-Transport-Security, Referrer-Policy, Permissions-Policy, Cross-Origin-Embedder-Policy, Cross-Origin-Opener-Policy, Cross-Origin-Resource-Policy) in the [server] section of install.ini, requiring a `dssadmin regenerate-config` run and a DSS restart to take effect.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>dip.properties &gt; dku.exports.disable*</t>
+          <t>Configure restrictive security HTTP headers like CSP, X-Frame-Options, and HSTS in install.ini.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>one_of</t>
+          <t>install.ini &gt; [server] content-security-policy / x-frame-options / x-content-type-options / x-xss-protection / hsts-max-age / referrer-policy / permissions-policy / cross-origin-embedder-policy / cross-origin-opener-policy / cross-origin-resource-policy</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>dku.exports.disableAllDatasetExports=true; dku.exports.disableAllDataExports=true; dku.exports.disableAllExports=true; dku.exports.disableCopySampleToClipboard=true; dku.exports.disableSQLNotebookCopyResultToClipboard=true</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>dku.exports.disableAllDatasetExports=true disables 'Download' export of datasets to files (CSV, Excel, Tableau Hyper, etc.), plus including datasets in project exports/bundle downloads and attaching datasets to emails in scenarios; other exports (ML data, schema, SQL queries, prepared data) remain possible. dku.exports.disableAllDataExports=true implies the previous key and additionally disables exports of prepared data or SQL query results, downloading files/zips from managed folders, and including datasets or managed folders in project exports/bundle downloads or scenario email attachments; ML data and schema exports remain possible. dku.exports.disableAllExports=true implies both previous keys and additionally disables exports of ML data and schemas, so essentially all dataset, prepared-data, SQL-query, ML data/schema, and managed-folder exports, downloads, bundle inclusions, and email attachments are disabled. dku.exports.disableCopySampleToClipboard=true disables copying data samples to the clipboard everywhere except SQL notebooks (default false, i.e. enabled). dku.exports.disableSQLNotebookCopyResultToClipboard=true disables copying results to the clipboard specifically in SQL notebooks (default false, i.e. enabled).</t>
-        </is>
-      </c>
+          <t>exists</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>restrictive values configured for each applicable header (e.g., x-frame-options=SAMEORIGIN, x-content-type-options=nosniff, hsts-max-age set to a non-zero value, a content-security-policy restricting sources)</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>dip.properties contains one or more of the five dku.exports.disable* keys set to true, at a scope level (dataset/data/all) matching the organization's data-exfiltration risk tolerance.</t>
+          <t>The source provides an example syntax but does not mandate one canonical value set for every header; presence of a restrictive, deliberately-chosen value for each relevant header indicates the practice is followed.</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>None of the dku.exports.disable* keys are present or set to true, meaning full export and clipboard-copy capabilities remain available to any user with data-view permission.</t>
+          <t>install.ini's [server] section contains one or more of these header keys with restrictive values (e.g., SAMEORIGIN/DENY for x-frame-options, nosniff for x-content-type-options, a non-trivial content-security-policy, hsts-max-age set).</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>dip.properties content is often not fully captured in diagnostics; if absent, flag as needs_manual_review. Importantly, even when these settings are enabled, treat this only as a risk-reduction control, not a guarantee: the source explicitly states export restriction is inherently 'best-effort' since a user who can view data can still exfiltrate it by other means (e.g., copy/paste).</t>
+          <t>The [server] section lacks these header keys entirely, meaning DSS is not emitting these security headers (browser defaults/no explicit protection).</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>Restricting export and clipboard-copy features reduces (but per the source's own warning, does not eliminate) the ability of authorized viewers to exfiltrate data out of DSS.</t>
+          <t>install.ini is a server-level config file often not captured in diagnostics; if absent, flag as needs_manual_review, since the default state (no headers configured) cannot otherwise be confirmed.</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>dip.properties, exports, data exfiltration</t>
+          <t>Configuring these headers hardens the DSS Web application against clickjacking, XSS, MIME-sniffing, protocol downgrade, and cross-origin data leakage attacks.</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
+          <t>install.ini, HTTP security headers, CSP, HSTS</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
           <t>advanced_security_options</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>6, 7, 8</t>
-        </is>
-      </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>Restricting exports; Restricting exports; Restricting exports</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
+          <t>Setting security-related HTTP headers</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U10" s="3" t="n"/>
       <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="n"/>
       <c r="X10" s="3" t="n"/>
       <c r="Y10" s="3" t="n"/>
       <c r="Z10" s="3" t="n"/>
+      <c r="AA10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -7580,7 +8030,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>must_have</t>
+          <t>nice_to_have</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -7590,91 +8040,96 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Transport &amp; Browser Hardening</t>
+          <t>Embedding &amp; Cookie Policy Tradeoffs</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Setting security-related HTTP headers</t>
+          <t>Allowing DSS to be hosted inside an iframe</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>DSS supports configuring standard security-related HTTP response headers (X-Frame-Options, Content-Security-Policy, X-XSS-Protection, X-Content-Type-Options, Strict-Transport-Security, Referrer-Policy, Permissions-Policy, Cross-Origin-Embedder-Policy, Cross-Origin-Opener-Policy, Cross-Origin-Resource-Policy) in the [server] section of install.ini, requiring a `dssadmin regenerate-config` run and a DSS restart to take effect.</t>
+          <t>By default DSS cannot be embedded in an iframe because browsers treat its authentication cookies as SameSite=Lax; enabling iframe embedding requires setting both security.sameSiteNoneCookies and security.secureCookies to true in general-settings.json, and requires DSS to be accessed exclusively via HTTPS (since browsers ignore SameSite=None on non-secure cookies).</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>install.ini &gt; [server] content-security-policy / x-frame-options / x-content-type-options / x-xss-protection / hsts-max-age / referrer-policy / permissions-policy / cross-origin-embedder-policy / cross-origin-opener-policy / cross-origin-resource-policy</t>
+          <t>Keep sameSiteNoneCookies disabled unless iframe embedding is a documented business need.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>exists</t>
+          <t>general-settings.json &gt; security.sameSiteNoneCookies</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>restrictive values configured for each applicable header (e.g., x-frame-options=SAMEORIGIN, x-content-type-options=nosniff, hsts-max-age set to a non-zero value, a content-security-policy restricting sources)</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>The source provides an example syntax but does not mandate one canonical value set for every header; presence of a restrictive, deliberately-chosen value for each relevant header indicates the practice is followed.</t>
-        </is>
-      </c>
+          <t>equals</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>false (secure default) unless a documented iframe-embedding need exists</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>install.ini's [server] section contains one or more of these header keys with restrictive values (e.g., SAMEORIGIN/DENY for x-frame-options, nosniff for x-content-type-options, a non-trivial content-security-policy, hsts-max-age set).</t>
+          <t>If enabled, security.secureCookies must also be true and DSS must be served exclusively over HTTPS; sameSiteNoneCookies=true without a documented business need for iframe embedding is a red flag.</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>The [server] section lacks these header keys entirely, meaning DSS is not emitting these security headers (browser defaults/no explicit protection).</t>
+          <t>general-settings.json "security" object omits sameSiteNoneCookies or sets it to false (secure default preserved).</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>install.ini is a server-level config file often not captured in diagnostics; if absent, flag as needs_manual_review, since the default state (no headers configured) cannot otherwise be confirmed.</t>
+          <t>sameSiteNoneCookies is set to true without secureCookies also being true and/or without confirmed exclusive HTTPS access, or is enabled with no documented iframe-embedding justification.</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Configuring these headers hardens the DSS Web application against clickjacking, XSS, MIME-sniffing, protocol downgrade, and cross-origin data leakage attacks.</t>
+          <t>If general-settings.json's security block is not present in the diagnosis, flag as needs_manual_review; the default assumption (disabled, DSS not embeddable) applies absent this key.</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>install.ini, HTTP security headers, CSP, HSTS</t>
+          <t>Allowing iframe embedding is only intended for specific integration scenarios; enabling it relaxes a cookie protection browsers use to mitigate certain cross-site attack vectors, so it should be a deliberate, justified choice.</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
+          <t>general-settings.json, security settings, cookies, iframe embedding, SameSite</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
           <t>advanced_security_options</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>Setting security-related HTTP headers</t>
+          <t>8, 9</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
+          <t>Allowing DSS to be hosted inside an iframe; Allowing DSS to be hosted inside an iframe</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U11" s="3" t="n"/>
       <c r="V11" s="3" t="n"/>
       <c r="W11" s="3" t="n"/>
       <c r="X11" s="3" t="n"/>
       <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
+      <c r="AA11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -7694,91 +8149,92 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Embedding &amp; Cookie Policy Tradeoffs</t>
+          <t>Content Rendering Hardening</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Allowing DSS to be hosted inside an iframe</t>
+          <t>Preventing links to be clickable in data tables</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>By default DSS cannot be embedded in an iframe because browsers treat its authentication cookies as SameSite=Lax; enabling iframe embedding requires setting both security.sameSiteNoneCookies and security.secureCookies to true in general-settings.json, and requires DSS to be accessed exclusively via HTTPS (since browsers ignore SameSite=None on non-secure cookies).</t>
+          <t>By default, DSS renders links as clickable in dataset Explore and dataset insights views; this can be disabled by setting dku.feature.dataTableLinks.enabled to false in dip.properties, preventing users from clicking potentially malicious or phishing links embedded within data content.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>general-settings.json &gt; security.sameSiteNoneCookies</t>
+          <t>Set dku.feature.dataTableLinks.enabled to false to stop clickable links in data tables.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
+          <t>dip.properties &gt; dku.feature.dataTableLinks.enabled</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>false (secure default) unless a documented iframe-embedding need exists</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>If enabled, security.secureCookies must also be true and DSS must be served exclusively over HTTPS; sameSiteNoneCookies=true without a documented business need for iframe embedding is a red flag.</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>general-settings.json "security" object omits sameSiteNoneCookies or sets it to false (secure default preserved).</t>
-        </is>
-      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>sameSiteNoneCookies is set to true without secureCookies also being true and/or without confirmed exclusive HTTPS access, or is enabled with no documented iframe-embedding justification.</t>
+          <t>dip.properties contains dku.feature.dataTableLinks.enabled=false.</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>If general-settings.json's security block is not present in the diagnosis, flag as needs_manual_review; the default assumption (disabled, DSS not embeddable) applies absent this key.</t>
+          <t>The key is absent (default true) or explicitly set to true, meaning links in data tables remain clickable.</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Allowing iframe embedding is only intended for specific integration scenarios; enabling it relaxes a cookie protection browsers use to mitigate certain cross-site attack vectors, so it should be a deliberate, justified choice.</t>
+          <t>If dip.properties content is not present in the diagnosis, flag as needs_manual_review; the default (links clickable) applies absent this key.</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>general-settings.json, security settings, cookies, iframe embedding, SameSite</t>
+          <t>Disabling clickable links in dataset Explore/insights reduces the risk that a malicious or phishing link embedded in data content could be inadvertently clicked by a user.</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
+          <t>dip.properties, dataset explore, phishing mitigation</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
           <t>advanced_security_options</t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t>8, 9</t>
-        </is>
-      </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>Allowing DSS to be hosted inside an iframe; Allowing DSS to be hosted inside an iframe</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
+          <t>Preventing links to be clickable in data tables</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="n"/>
       <c r="W12" s="3" t="n"/>
       <c r="X12" s="3" t="n"/>
       <c r="Y12" s="3" t="n"/>
       <c r="Z12" s="3" t="n"/>
+      <c r="AA12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -7798,191 +8254,96 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Content Rendering Hardening</t>
+          <t>Identity Integrity &amp; Impersonation Prevention</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Preventing links to be clickable in data tables</t>
+          <t>Allowing DSS users to edit their display names and emails</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>By default, DSS renders links as clickable in dataset Explore and dataset insights views; this can be disabled by setting dku.feature.dataTableLinks.enabled to false in dip.properties, preventing users from clicking potentially malicious or phishing links embedded within data content.</t>
+          <t>Since DSS 13.2.0, only administrators can edit users' display names and email addresses by default, specifically to prevent impersonation; enabling security.enableEmailAndDisplayNameModification (true) in general-settings.json lets users self-service these fields but also disables the ability for users to share assets (e.g., projects) via email invitations, so DSS should not have this enabled unless there is a specific, documented business need.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>dip.properties &gt; dku.feature.dataTableLinks.enabled</t>
+          <t>Keep enableEmailAndDisplayNameModification disabled so only admins edit display names and emails.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
+          <t>general-settings.json &gt; security.enableEmailAndDisplayNameModification</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
           <t>equals</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="n"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>false (secure default) unless documented otherwise</t>
+        </is>
+      </c>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>dip.properties contains dku.feature.dataTableLinks.enabled=false.</t>
+          <t>If true, email-invitation-based asset sharing (e.g., project sharing via email invite) is disabled as a side effect; enabling should only be done for a specific, documented business need.</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>The key is absent (default true) or explicitly set to true, meaning links in data tables remain clickable.</t>
+          <t>general-settings.json "security" object omits enableEmailAndDisplayNameModification or sets it to false, meaning only admins can edit user display names/emails (impersonation risk minimized).</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>If dip.properties content is not present in the diagnosis, flag as needs_manual_review; the default (links clickable) applies absent this key.</t>
+          <t>enableEmailAndDisplayNameModification is set to true without a documented business justification, allowing users to self-service edit their display name/email (impersonation risk, and email-invitation sharing disabled).</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Disabling clickable links in dataset Explore/insights reduces the risk that a malicious or phishing link embedded in data content could be inadvertently clicked by a user.</t>
+          <t>If general-settings.json's security block is not present in the diagnosis, flag as needs_manual_review; the post-13.2.0 default (self-edit disabled) should be assumed absent evidence otherwise.</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>dip.properties, dataset explore, phishing mitigation</t>
+          <t>This restriction (default since 13.2.0) helps prevent impersonation by DSS users; enabling self-edit trades that protection for convenience and disables the email-invitation sharing feature.</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
+          <t>general-settings.json, security settings, user identity, impersonation prevention, sharing</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
           <t>advanced_security_options</t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>Preventing links to be clickable in data tables</t>
+          <t>9, 10</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
+          <t>Allowing DSS users to edit their display names and emails; Allowing DSS users to edit their display names and emails</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="U13" s="3" t="n"/>
       <c r="V13" s="3" t="n"/>
       <c r="W13" s="3" t="n"/>
       <c r="X13" s="3" t="n"/>
       <c r="Y13" s="3" t="n"/>
       <c r="Z13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>ADVSEC-013</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>nice_to_have</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>specific_setting</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Identity Integrity &amp; Impersonation Prevention</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Allowing DSS users to edit their display names and emails</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Since DSS 13.2.0, only administrators can edit users' display names and email addresses by default, specifically to prevent impersonation; enabling security.enableEmailAndDisplayNameModification (true) in general-settings.json lets users self-service these fields but also disables the ability for users to share assets (e.g., projects) via email invitations, so DSS should not have this enabled unless there is a specific, documented business need.</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>general-settings.json &gt; security.enableEmailAndDisplayNameModification</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>equals</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>false (secure default) unless documented otherwise</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>If true, email-invitation-based asset sharing (e.g., project sharing via email invite) is disabled as a side effect; enabling should only be done for a specific, documented business need.</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>general-settings.json "security" object omits enableEmailAndDisplayNameModification or sets it to false, meaning only admins can edit user display names/emails (impersonation risk minimized).</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>enableEmailAndDisplayNameModification is set to true without a documented business justification, allowing users to self-service edit their display name/email (impersonation risk, and email-invitation sharing disabled).</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>If general-settings.json's security block is not present in the diagnosis, flag as needs_manual_review; the post-13.2.0 default (self-edit disabled) should be assumed absent evidence otherwise.</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>This restriction (default since 13.2.0) helps prevent impersonation by DSS users; enabling self-edit trades that protection for convenience and disables the email-invitation sharing feature.</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>general-settings.json, security settings, user identity, impersonation prevention, sharing</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>advanced_security_options</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>9, 10</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>Allowing DSS users to edit their display names and emails; Allowing DSS users to edit their display names and emails</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="n"/>
-      <c r="Y14" s="3" t="n"/>
-      <c r="Z14" s="3" t="n"/>
+      <c r="AA13" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/skills/dataiku-diagnosis-checklist-review/resources/checklist_template.xlsx
+++ b/skills/dataiku-diagnosis-checklist-review/resources/checklist_template.xlsx
@@ -4122,7 +4122,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>general-settings.json &gt; llmTraceSettings.traceExplorerDefaultWebApp</t>
+          <t>general-settings.json &gt; generativeAISettings &gt; llmTraceSettings.traceExplorerDefaultWebApp</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -4139,7 +4139,7 @@
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>llmTraceSettings.traceExplorerDefaultWebApp present in general-settings.json with non-empty projectKey and webAppId fields.</t>
+          <t>generativeAISettings.llmTraceSettings.traceExplorerDefaultWebApp present in general-settings.json with non-empty projectKey and webAppId fields.</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">

--- a/skills/dataiku-diagnosis-checklist-review/resources/checklist_template.xlsx
+++ b/skills/dataiku-diagnosis-checklist-review/resources/checklist_template.xlsx
@@ -1395,7 +1395,11 @@
           <t>high</t>
         </is>
       </c>
-      <c r="V9" s="3" t="n"/>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>Worded for Spark on Kubernetes (executor pods). If no Kubernetes cluster is attached and Spark runs on YARN/Hadoop, the pod-based checks do not apply.</t>
+        </is>
+      </c>
       <c r="W9" s="3" t="n"/>
       <c r="X9" s="3" t="n"/>
       <c r="Y9" s="3" t="n"/>
@@ -7289,7 +7293,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management &gt; Maximum session duration / Idle timeout</t>
+          <t>general-settings.json &gt; security.sessionsMaxTotalTimeMinutes / security.sessionsMaxIdleTimeMinutes (UI: Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management)</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -7299,28 +7303,28 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>configured to a finite, non-default timeout value</t>
+          <t>either value set to a finite number of minutes greater than 0</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>The source does not mandate a specific numeric threshold, only that admins may configure these fields; treat as satisfied if either or both values are set to a finite duration rather than left unlimited/unset.</t>
+          <t>In general-settings.json a value of 0 means unlimited (the default). The source does not mandate a specific threshold; treat as satisfied if either or both values are greater than 0.</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Diagnosis or exported settings show a configured, finite 'Maximum session duration' and/or 'Idle timeout' value in session management settings.</t>
+          <t>general-settings.json security.sessionsMaxTotalTimeMinutes and/or security.sessionsMaxIdleTimeMinutes is greater than 0.</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Session management settings show these fields unset or set to unlimited/no-expiration.</t>
+          <t>Both keys are 0 (unlimited) or absent.</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Session management configuration is often not captured in standard diagnostic exports (it's a UI/DB-stored setting, not a config file key); flag as needs_manual_review, noting the source's own caveat about potential lost work from expiring sessions.</t>
+          <t>Flag needs_manual_review only if general-settings.json or its security block is not in the diagnosis; otherwise decide from the two keys. Note the source's caveat that expiring sessions can lose in-progress work.</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -7355,7 +7359,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>No literal config-file key is given for this UI-only setting, and no specific recommended numeric threshold is provided, so the expected_condition is a best-effort conceptual pointer to the UI path rather than a literal field.</t>
+          <t>The source gives only the UI path and no numeric threshold; the file keys were verified against sample bundles, not the source documents.</t>
         </is>
       </c>
       <c r="W4" s="3" t="n"/>
@@ -7402,7 +7406,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management &gt; Force single session per user</t>
+          <t>general-settings.json &gt; security.forceSingleSessionPerUser (UI: Administration &gt; Settings &gt; Security &amp; Audit &gt; User login &amp; provisioning &gt; Session management &gt; Force single session per user)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -7412,28 +7416,28 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>This is a UI toggle, not a documented general-settings.json/dip.properties key in the source text.</t>
+          <t>Default is false (multiple concurrent sessions allowed).</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Session management settings show 'Force single session per user' enabled.</t>
+          <t>general-settings.json security.forceSingleSessionPerUser is true.</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>The setting is shown as disabled (default), allowing multiple concurrent sessions per user.</t>
+          <t>security.forceSingleSessionPerUser is false (default) or absent, allowing multiple concurrent sessions per user.</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>This UI-only toggle is often not captured in diagnostic exports; flag as needs_manual_review, noting the default is disabled (multiple sessions allowed).</t>
+          <t>Flag needs_manual_review only if general-settings.json or its security block is not in the diagnosis; otherwise decide from the key.</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -7468,7 +7472,7 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>No literal config-file key is given for this UI-only setting.</t>
+          <t>The source gives only the UI path; the file key was verified against sample bundles, not the source documents.</t>
         </is>
       </c>
       <c r="W5" s="3" t="n"/>
@@ -8169,34 +8173,34 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>dip.properties &gt; dku.feature.dataTableLinks.enabled</t>
+          <t>general-settings.json &gt; security.disableDataTableLinks, or dip.properties &gt; dku.feature.dataTableLinks.enabled</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>equals</t>
+          <t>one_of</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>disableDataTableLinks = true, or dataTableLinks.enabled = false</t>
         </is>
       </c>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>dip.properties contains dku.feature.dataTableLinks.enabled=false.</t>
+          <t>general-settings.json security.disableDataTableLinks is true, or dip.properties contains dku.feature.dataTableLinks.enabled=false.</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>The key is absent (default true) or explicitly set to true, meaning links in data tables remain clickable.</t>
+          <t>security.disableDataTableLinks is false and the dip.properties key is absent (default: links clickable) or true.</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>If dip.properties content is not present in the diagnosis, flag as needs_manual_review; the default (links clickable) applies absent this key.</t>
+          <t>Check both general-settings.json and dip.properties before flagging needs_manual_review; the default (links clickable) applies when neither sets it.</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -8229,7 +8233,11 @@
           <t>high</t>
         </is>
       </c>
-      <c r="V12" s="3" t="n"/>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>That disableDataTableLinks is the general-settings counterpart of dku.feature.dataTableLinks.enabled is inferred from the key names; the source documents only the property.</t>
+        </is>
+      </c>
       <c r="W12" s="3" t="n"/>
       <c r="X12" s="3" t="n"/>
       <c r="Y12" s="3" t="n"/>
